--- a/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
+++ b/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개요" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무공간" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정보구조도" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="트윈유형" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데모동선" sheetId="5" state="visible" r:id="rId5"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-10 22:41 생성). 값이 갈리면 md 가 이긴다</t>
+          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-11 11:52 생성). 값이 갈리면 md 가 이긴다</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IA 기준안 - 재검수 잔여항목 반영 완료·엑셀 동기화 필요</t>
+          <t>IA 기준안 - 재검수 잔여항목 반영·엑셀 동기화 완료</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Phase 2의 업무 공간, 화면 역할, 정보 객체, 대표 데모 동선과 기존 화면 판정을 정의한다.</t>
+          <t>Phase 2의 화면 구성, 화면 역할, 정보 객체, 대표 데모 동선과 기존 화면 판정을 정의한다.</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CUVIA_NDMS_기능및정보구조도.xlsx는 이 MD의 내용을 업무 검토용 표로 옮긴 동기화본이다. 개요, 업무공간, 정보구조도, 트윈유형, 데모동선, 사건맥락, 정보객체, 공통상태, Phase1판정, 데모범위의 10개 시트로 구성한다.</t>
+          <t>CUVIA_NDMS_기능및정보구조도.xlsx는 이 MD의 내용을 업무 검토용 표로 옮긴 동기화본이다. 개요, 화면, 정보구조도, 트윈유형, 데모동선, 사건맥락, 정보객체, 공통상태, Phase1판정, 데모범위의 10개 시트로 구성한다.</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>각 업무 공간은 담당자의 한 가지 핵심 질문에 답한다.</t>
+          <t>각 화면은 담당자의 한 가지 핵심 질문에 답한다.</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>사건 ID, 기준시각, 처리상태, 선택 예측판·영향공간·근거, 검토 중 결정, 사건 시나리오 방식과 이벤트별 수집·시연 방식은 화면을 이동해도 유지한다.</t>
+          <t>사건 ID, 기준시각, 처리상태, 선택 예측판·영향공간·근거와 검토 중 결정은 화면을 이동해도 유지한다. 사건 시나리오 방식과 이벤트별 수집·시연 방식은 내부 계약으로 유지한다.</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>정직한 상태</t>
+          <t>제품에 필요한 근거</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>연계 준비도, 시연 방식, 데이터 품질과 계산 주체를 표시한다.</t>
+          <t>관측·갱신시각, 품질, 출처기관, 예측 기준시각과 모델처럼 담당자의 판단에 필요한 정보만 화면에 표시한다. 데모 fixture의 실제·시나리오 구분과 교체 대상은 내부에서 관리한다.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>다섯 업무 공간이 각각 하나의 핵심 질문에 답한다.</t>
+          <t>화면 넷과 디지털트윈이 각각 하나의 핵심 질문에 답하고, 대응 모의훈련은 D8 진입점에서 후속 확장된다.</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>사건 ID, 기준시각, 처리상태, 선택 예측판·영향공간·근거, 검토 중 결정, 사건 시나리오 방식과 이벤트별 dataOrigin·수집·시연 방식이 화면 이동 중 유지된다.</t>
+          <t>사건 ID, 기준시각, 처리상태, 선택 예측판·영향공간·근거와 검토 중 결정이 제품 화면의 사건 맥락으로 유지된다. 사건 시나리오 방식과 이벤트별 dataOrigin·수집·시연 방식은 내부 사건 맥락과 계약으로 유지하되, 제작 구분을 위한 표시를 기본 제품 UI에 노출하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>실시간·재생·모의·수동 및 품질 표시</t>
+          <t>관측·갱신시각, 품질, 출처기관과 예측 기준시각·모델 등 제품에 필요한 근거 표시</t>
         </is>
       </c>
     </row>
@@ -1096,223 +1096,223 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IA-05의 대응 모의훈련 시나리오 후보 진입점. 훈련 편집·실행 화면은 만들지 않음</t>
+          <t>예측 이벤트를 누르면 사건 지도가 디지털트윈 화면으로 바뀌는 흐름과 대안 선택</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 데모 구현 시 반드시 포함할 핵심</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
+          <t>D8의 대응 모의훈련 진입점. A 시나리오 목록·실행은 일정이 허용할 때 선택 에필로그로 구현하고 편집·예약과 C 훈련은 제외</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>기준·대안 예측판 비교</t>
+          <t>A 대응 모의훈련 목록·실행 에필로그. 편집·예약과 C 유형 훈련은 후속 범위</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>영향 대상과 실제 SOP·전파문 연결</t>
+          <t>C 해안 월류의 시나리오 Forecast 기반 모의 예측 화면(R1)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>예측과 실제 관측의 오차 검증</t>
+          <t>D 산불·F 지반의 정적 개념 예시(R0)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 이때 IA-03은 비활성 빈 화면으로 숨기지 않고 미확보 조건을 표시하며 모델 성능이나 대안 효과를 주장하지 않는다. 합성 결과임은 화면 배지가 아니라 사건 헤더의 데이터 상태 칩과 시연 대본이 든다.</t>
+          <t>G 펌프 장애가 독립 고장 기준을 넘을 때 별도 사건으로 분리되는 관계 표시</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>모든 유형의 동적 모델</t>
+          <t>기록·검증 정리, 사건 AI 보조 오버레이와 운영 관리 보조 구조</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>실제 재난문자·시설 원격제어</t>
+          <t>C 모의 예측과 G 파생 장면은 제품 방향에는 포함하되 대표 도시침수 D0~D8의 완료 조건에는 넣지 않는다. 항목별 일정과 시연 효과를 확인해 I4에서 선택한다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
+          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련 시나리오 편집·실행·예약 화면</t>
+          <t>기준·대안 예측판 비교</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>대규모 운영 통계와 SLA</t>
+          <t>영향 대상과 실제 SOP·전파문 연결</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
+          <t>예측과 실제 관측의 오차 검증</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
+          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 디지털트윈 화면은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하며 기본 제품 UI에 제작 설명을 노출하지 않는다. 검증되지 않은 모델 성능이나 실제 운영 성과로 대외 주장하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>답할 사용자 질문</t>
+          <t>모든 유형의 동적 모델</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>사용하는 공통 객체와 필드</t>
+          <t>실제 재난문자·시설 원격제어</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>진입 조건과 다음 행동</t>
+          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>시스템 생성 정보와 담당자 결정의 구분</t>
+          <t>대응 모의훈련 시나리오 편집·예약과 C 유형 훈련. A 목록·실행은 선택 에필로그 IA-T01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>정상·빈·지연·결측·모의·실패 상태</t>
+          <t>대규모 운영 통계와 SLA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>데이터·모델·업무 근거와 준비도</t>
+          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>대표 데모 포함 여부</t>
+          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
         </is>
       </c>
     </row>
@@ -1336,91 +1336,91 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>기존 자산의 재사용·재편·제외 판정</t>
+          <t>답할 사용자 질문</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>다음은 현재 기준안에서 결정됐다.</t>
+          <t>사용하는 공통 객체와 필드</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 사건 우선 큐에 나타나면 IA-02로 연다.</t>
+          <t>진입 조건과 다음 행동</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
+          <t>시스템 생성 정보와 담당자 결정의 구분</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다.</t>
+          <t>정상·빈·지연·결측·실패 상태와 내부 시나리오 처리</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>P0 자료 확인 전 IA-03은 합성 예측면으로 흐름을 보여주고, 실제 모델 결과가 아님은 시연 대본이 밝힌다.</t>
+          <t>데이터·모델·업무 근거와 준비도</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>IA-02는 Phase 1 지구 재난관제 팝업의 개요 고정·탭 골조를 유지하고 내용을 사건 개요·근거·영상·관계 이력 중심으로 재편한다.</t>
+          <t>대표 데모 포함 여부</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>IA-03은 사건 맥락을 유지하는 독립 페이지로 열고, IA-04 대응은 사건 화면 안 팝업으로 둔다.</t>
+          <t>기존 자산의 재사용·재편·제외 판정</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>IA-05는 상시 접근 가능한 독립 페이지로 두되 대표 데모의 주 동선에서는 D8에 진입한다.</t>
+          <t>다음은 현재 기준안에서 결정됐다.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C·D·F 비교는 IA-03 유형 전환으로 제시하고 R0인 D·F는 정적 개념 예시와 필요한 근거만 보여준다.</t>
+          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 사건 우선 큐에 나타나면 IA-02로 연다.</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>IA-05의 대응 이력은 후속 대응 모의훈련 시나리오의 입력이 될 수 있다. 훈련 편집·실행은 운영 관리 범위이자 대표 데모 밖이며, 훈련 조건을 트윈의 사전 조건분석 진입점으로 연결할 수 있다.</t>
+          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>남은 확인은 다음 두 가지다.</t>
+          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Phase 1 경로를 재사용할 때 IA-03 독립 페이지의 최종 URL과 사건 ID 전달 방식을 구현 설계에서 확정한다.</t>
+          <t>P0 자료 확인 전 IA-03은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하고, 기본 제품 UI에 제작 설명을 넣지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,103 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>실제 기관의 메뉴 권한과 운영 절차를 확인해 IA-05 상시 접근 권한과 훈련 관리 책임 조직을 정한다.</t>
+          <t>IA-02는 Phase 1 지구 재난관제 팝업의 개요 고정·탭 골조를 유지하고 내용을 사건 개요·근거·영상·관계 이력 중심으로 재편한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>IA-03 디지털트윈은 독립 페이지가 아니라 사건 작업공간 안에서 예측 이벤트를 눌러 여는 디지털트윈 화면이다. IA-04 대응은 사건 화면 안 팝업으로 둔다. (2026-09-10 저녁 변경. 이전 결정은 독립 페이지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>IA-05는 상시 접근 가능한 독립 페이지로 두되 대표 데모의 주 동선에서는 D8에 진입한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>C·D·F 비교는 IA-03 유형 전환으로 설계한다. C 모의 예측과 R0인 D·F 정적 개념 예시는 I4 선택 범위다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>G 파생 관계 표시도 I4 선택 범위다. 대표 데모 필수 범위는 도시침수 D0~D8과 D8의 TrainingScenario 생성 진입점·전달 계약까지다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>대응 모의훈련은 사이드바 메뉴(IA-T01)로 설계한다. D8 진입점은 포함하고, 일정이 허용하면 A 시나리오 목록과 실행을 선택 에필로그로 만든다. 편집·예약과 C 유형 훈련은 후속 범위다. 실행 화면은 Phase 1 트윈 페이지를 사전 조건분석으로 쓰며 IA-05의 대응 이력이 시나리오의 입력이 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>남은 확인은 다음 두 가지다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>선택 에필로그를 구현할 경우 D8 원 사건에서 IA-T01 훈련 시나리오를 생성할 입력·참조 ID 계약을 구현 설계에서 확정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>실제 기관의 메뉴 권한과 운영 절차를 확인해 IA-05 상시 접근 권한과 훈련 관리 책임 조직을 정한다. 이번 데모에서는 확정하지 않고 추후 제품 개발 시 정의한다.</t>
         </is>
       </c>
     </row>
@@ -1507,17 +1603,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1533,30 +1631,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>제공 형태</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>기준 라우트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>담당자의 핵심 질문</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>대표 산출물</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>데모 위치</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>하위 구성 (§4)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>주 진입 조건 (§5.1)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>다음 행동 (§5.1)</t>
         </is>
@@ -1575,30 +1683,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>상시 메뉴·독립 화면</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>/incidents</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>지금 무엇을 먼저 확인해야 하는가?</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>감시 우선대상·사건·후보 목록</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>D0 진입</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>감시 우선대상·사건 후보·사건 우선 큐</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>업무 시작 또는 D0 감시 우선대상 갱신</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>감시 대상 확인, D1 후보가 생기면 사건 열기</t>
         </is>
@@ -1617,32 +1731,38 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>사건 선택 후 여는 중심 화면</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>왜 같은 사건이며 무엇을 더 확인해야 하는가?</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>확인된 사건과 근거 묶음</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>D1~D3 핵심</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>사건 개요 / 관측 근거 / 영상·현장 / 상태·관계 이력</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>후보 선택, 관련 사건 링크 또는 검토 요청</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>확인·오탐·병합·분리 후 트윈 비교 또는 대응 검토</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>확인·오탐·병합·분리 후 디지털트윈 또는 대응 검토</t>
         </is>
       </c>
     </row>
@@ -1654,37 +1774,43 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>IA-02 지도 영역의 예측 모드</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/twin</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>그대로 두면 어떻게 되고 대안은 무엇인가?</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>기준·대안 예측판과 영향</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>D4~D5 핵심</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>현재 상태 / 기준 전망 / 대안 전망 / 영향·근거·한계</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>확인된 사건과 기준 예측판(실제 또는 합성) 선택</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>예측판·영향공간·근거를 선택해 대응 검토 시작</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>사건 화면의 근거 목록이나 타임라인에서 예측 이벤트 선택</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>시각·대안을 고르고 [이 전망으로 대응 검토]로 대응 검토 시작</t>
         </is>
       </c>
     </row>
@@ -1701,30 +1827,36 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>사건 맥락을 유지하는 팝업·패널</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/response</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>무엇을 승인하고 실제로 되었는가?</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>대응 결정과 실행 결과</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>D6~D7 핵심</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>권고·SOP / 승인·전파·시설 요청 / 채널·현장 실행 결과</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>영향 근거와 검토할 권고·결정안 존재</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>승인·실행 결과를 추적하고 대응중·통제로 전환</t>
         </is>
@@ -1743,30 +1875,36 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>상시 메뉴·독립 화면</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>/records, /records/:incidentId</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>무엇을 예측·결정했고 실제 결과는 어땠는가?</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>사건 기록·검증·보고서</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>D8 종료</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>사건 타임라인 / 예측 대 실제 / 상황보고서·개선 항목</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>통제·종료 사건 또는 과거 사건 조회</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>검증·보고서·개선 항목 확정, 필요하면 사건 재개</t>
         </is>
@@ -1775,76 +1913,146 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-T01</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AI 보조</t>
+          <t>대응 모의훈련</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>현재 사건의 근거를 어떻게 빨리 찾는가?</t>
+          <t>사이드바 메뉴·독립 훈련 흐름</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>근거 요약·해당 위치 이동</t>
+          <t>/drills, /drills/:scenarioId/run</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>이 조건이면 어떻게 대응할 것인가?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>훈련 진입점, 선택 시 A 시나리오 목록·실행·이력</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>선택 에필로그</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>D8 진입점 또는 선택 에필로그의 A 훈련 시나리오 선택</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>디지털트윈 화면(사전 조건분석)에서 대응 연습, 훈련 이력 기록</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AI 보조</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>현재 화면 위 공통 보조</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>별도 라우트 없음</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>현재 사건의 근거를 어떻게 빨리 찾는가?</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>근거 요약·해당 위치 이동</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>IA-A01</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>운영 관리</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>관리자 메뉴</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>/admin/*</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>기준·SOP·연계 대상을 어떻게 관리하는가?</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>운영 설정</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>데모 밖</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>IA ID는 설계상 식별자이며 기존 SCR 번호나 최종 URL을 뜻하지 않는다.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1857,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1876,7 +2084,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>업무 공간</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2327,7 +2535,7 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>사건 후보가 왜 만들어졌는지 확인하고, 담당자가 실제 사건 여부와 관계를 결정하는 중심 업무 공간이다.</t>
+          <t>사건 후보가 왜 만들어졌는지 확인하고, 담당자가 실제 사건 여부와 관계를 결정하는 중심 화면이다.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -2490,12 +2698,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>데이터 표시</t>
+          <t>운영 근거</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>dataOrigin, 연계 준비도, 시연 방식, 품질, 계산 주체</t>
+          <t>관측·갱신시각, 품질, 출처기관, 예측 기준시각·모델 등 실제 판단에 필요한 정보</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -2826,12 +3034,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>영상·현장</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>사건 주변 CCTV와 선택 영상</t>
+          <t>침수예측판 갱신(E8)을 관측·영상과 같은 급의 근거로. 유효 시각·침수심·영향 요약 한 줄과 [디지털트윈 보기]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2859,7 +3067,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>VLM 분석 문장, 신뢰도, 모델·버전·분석시각</t>
+          <t>사건 주변 CCTV와 선택 영상</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2887,7 +3095,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>실제 영상과 분석 결과 병렬 확인</t>
+          <t>VLM 분석 문장, 신뢰도, 모델·버전·분석시각</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2915,7 +3123,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>현장 보고·사진·통행 가능 여부</t>
+          <t>실제 영상과 분석 결과 병렬 확인</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2938,12 +3146,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>상태·관계 이력</t>
+          <t>영상·현장</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>후보 생성·확인·오탐·병합·분리 기록</t>
+          <t>현장 보고·사진·통행 가능 여부</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2971,7 +3179,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>상태 변경 사유와 담당자</t>
+          <t>후보 생성·확인·오탐·병합·분리 기록</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2999,7 +3207,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>외부 기관 사건과의 관계</t>
+          <t>상태 변경 사유와 담당자</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -3017,13 +3225,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>상태·관계 이력</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>확인, 추가 확인, 오탐</t>
+          <t>외부 기관 사건과의 관계</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3041,13 +3253,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>상태·관계 이력</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>기존 사건에 병합 또는 별도 사건으로 분리</t>
+          <t>타임라인에 예측 유효 시각의 미래 눈금</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3071,7 +3287,7 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원인·파생·동시발생 관계 지정</t>
+          <t>확인, 추가 확인, 오탐</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3095,7 +3311,7 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>이후 트윈·대응에서 유지할 관측·영상·분석 근거 선택</t>
+          <t>기존 사건에 병합 또는 별도 사건으로 분리</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -3119,7 +3335,7 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교 열기</t>
+          <t>원인·파생·동시발생 관계 지정</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -3143,7 +3359,7 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>대응 검토 시작</t>
+          <t>이후 트윈·대응에서 유지할 관측·영상·분석 근거 선택</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3151,23 +3367,23 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>현재 상태와 미래 전망을 구분하고, 조건을 바꿨을 때 영향이 어떻게 달라지는지 비교한다.</t>
+          <t>예측 이벤트를 눌러 디지털트윈 열기. 같은 화면의 지도가 디지털트윈 화면으로 바뀐다</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3175,34 +3391,26 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>현재 상태</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>지금 실제로 관측된 것은 무엇인가?</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>관측값·시설상태·영상·품질·기준시각</t>
-        </is>
-      </c>
+          <t>대응 검토 시작</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3212,29 +3420,21 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>기준 전망</t>
-        </is>
-      </c>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>현재 조건이 유지되면 어떻게 되는가?</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>유효시간별 공간 결과·도달시간·강도</t>
-        </is>
-      </c>
+          <t>사건 작업공간 안의 디지털트윈 화면이다. 담당자가 근거 목록이나 타임라인의 예측 이벤트를 누르면 같은 지도가 그 시각의 3D 디지털트윈 화면으로 바뀐다. 독립 페이지가 아니다. 현재 상태와 미래 전망을 구분하고, 조건을 바꿨을 때 영향이 어떻게 달라지는지 비교한다. 대응 모의훈련(IA-T01)이 같은 디지털트윈 화면을 사건 없이 사용한다.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3244,27 +3444,27 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
+          <t>구성 요소</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>대안 전망</t>
+          <t>3D 지도</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>무엇을 바꾸었고 무엇이 달라지는가?</t>
+          <t>지도가 3D로 전환되고 지형·건물 위에 시간대별 침수심과 영향 대상(도로·건물·대상자)이 표시된다</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>변경 조건·기준 대비 차이</t>
+          <t>트윈 페이지 3D 씬. 수면 하나를 배수권역 단위 침수심으로, 영향 대상 표시 추가</t>
         </is>
       </c>
     </row>
@@ -3276,27 +3476,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
+          <t>구성 요소</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>영향 결과</t>
+          <t>시간 조절</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>누가·어디가·언제 영향을 받는가?</t>
+          <t>예측 시각을 옮긴다. 눈금은 예측판 유효 시각, 남은 시간 표시</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>도로·건물·시설·대상·노출·중단</t>
+          <t>시간축 패널</t>
         </is>
       </c>
     </row>
@@ -3308,27 +3508,27 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
+          <t>구성 요소</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>근거·한계</t>
+          <t>대안 선택</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>무엇으로 계산했고 어디까지 믿을 수 있는가?</t>
+          <t>그대로 / 도로 통제 / 배수 대응</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·입력·가정·불확실성·결측</t>
+          <t>신설</t>
         </is>
       </c>
     </row>
@@ -3340,21 +3540,29 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>배수권역·관로망·센서·CCTV 위치</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+          <t>기준 전망과 대안 전망의 2열 비교</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과 카드. 열 제목만 바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3364,21 +3572,29 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>근거·한계</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>현재 강우·관로·도로수위·조위·펌프·저류시설 가용성</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>모델·버전·입력·기준시각·품질·가정</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>근거 카드에 항목 추가</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3388,18 +3604,18 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
+          <t>구성 요소</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>시간대별 침수심·범위·도달시간</t>
+          <t>시연 시각 이후에 실제로 일어난 일은 눈금에 넣지 않는다. 판단에 쓰는 값은 눈금값이고 눈금 사이 값은 "사용자가 고른 시각"으로 구분한다.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3412,21 +3628,29 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>기준 전망과, 데이터가 있을 때의 배수·통제 대안</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+          <t>지금 실제로 관측된 것은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>관측값·시설상태·영상·품질·기준시각</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3436,21 +3660,29 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>기준 전망</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>도로·건물·중요시설·대상자 영향</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>현재 조건이 유지되면 어떻게 되는가?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>유효시간별 공간 결과·도달시간·강도</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3460,21 +3692,29 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>대안 전망</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>외부 모델 수신인지 CUVIA 계산인지 구분</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
+          <t>무엇을 바꾸었고 무엇이 달라지는가?</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>변경 조건·기준 대비 차이</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3484,21 +3724,29 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>기준 전망 선택과 유효시간별 결과 이동</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
+          <t>누가·어디가·언제 영향을 받는가?</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>도로·건물·시설·대상·노출·중단</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3508,21 +3756,29 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>근거·한계</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>지원되는 대안 조건 선택과 실행 요청, 또는 수신된 대안 예측판 선택</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+          <t>무엇으로 계산했고 어디까지 믿을 수 있는가?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>모델·버전·입력·가정·불확실성·결측</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3532,18 +3788,18 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>영향공간과 그 결과를 만든 근거 선택</t>
+          <t>배수권역·관로망·센서·CCTV 위치</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3556,18 +3812,18 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>기준 대비 차이와 불확실성 확인</t>
+          <t>현재 강우·관로·도로수위·조위·펌프·저류시설 가용성</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3580,18 +3836,18 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>선택한 예측판·영향공간을 유지한 채 대응 검토 시작</t>
+          <t>시간대별 침수심·범위·도달시간</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3604,18 +3860,18 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>유형별 교체 영역</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
+          <t>기준 전망과, 데이터가 있을 때의 배수·통제 대안</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3628,18 +3884,18 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>유형별 교체 영역</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
+          <t>도로·건물·중요시설·대상자 영향</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3652,18 +3908,18 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>기준 전망이 없으면 예측을 가장하지 않고 필요한 모델·데이터를 표시한다.</t>
+          <t>외부 모델 수신인지 CUVIA 계산인지 구분</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3676,18 +3932,18 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>제품 범위상 지원하지 않거나 실행하지 않은 대안은 계산 미지원·미실행, 필요한 입력이 없어 산출할 수 없으면 대안 계산 불가, 실행 중 오류가 난 경우는 계산 실패로 구분한다.</t>
+          <t>근거 목록·타임라인의 예측 이벤트 선택</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3700,18 +3956,18 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>실제 관측 비교가 없으면 검증 대기 상태와 필요한 결과를 표시한다.</t>
+          <t>시간 조절로 유효 시각 이동</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3724,18 +3980,18 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>트윈 비교</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>임의 슬라이더로 침수면을 움직인 장면을 예측이라고 부르지 않는다.</t>
+          <t>대안 선택(그대로 / 도로 통제 / 배수 대응)으로 기준 대 대안 비교</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -3743,23 +3999,23 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>예측과 영향 근거를 실제 결정, 승인, 전파·시설 요청과 결과로 연결한다.</t>
+          <t>영향공간과 그 결과를 만든 근거 선택</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -3767,27 +4023,23 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>판단 요약</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>IA-02에서 확정한 위험판단과 영향, 불확실성·반대 근거의 대응용 요약</t>
+          <t>[이 전망으로 대응 검토]: 선택한 시각·대안을 가지고 대응 팝업을 연다. 권고 카드에 전망 기준이 표시된다</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -3795,27 +4047,23 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>권고</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>권고 대응수준, 대상, 시점, 생성 근거</t>
+          <t>긴급 시 디지털트윈 화면을 열지 않고 대응 검토로 갈 수 있다</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -3823,27 +4071,23 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>SOP 초안</t>
-        </is>
-      </c>
+          <t>유형별 교체 영역</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>단계별 업무, 담당 조직, 자동/승인 구분</t>
+          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -3851,27 +4095,23 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
+          <t>유형별 교체 영역</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>선택안, 수정사항, 승인자·시각·사유</t>
+          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -3879,27 +4119,23 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>실행</t>
-        </is>
-      </c>
+          <t>데이터가 없을 때</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>전파(CAP 1.2 필드 구조)·도로통제·시설점검·운영 요청</t>
+          <t>기준 전망이 없으면 예측을 가장하지 않고 필요한 모델·데이터를 표시한다.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -3907,27 +4143,23 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
+          <t>데이터가 없을 때</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소</t>
+          <t>지원하지 않는 대안은 대안 선택에 나타나지 않는다. 미지원·미실행·실패는 ModelRun 상태값으로만 기록하고 화면 라벨로 두지 않는다.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -3935,23 +4167,23 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>권고 검토·수정·기각</t>
+          <t>실제 관측 비교가 없으면 검증 대기 상태와 필요한 결과를 표시한다.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -3959,23 +4191,23 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>SOP 항목 선택 및 담당 배정</t>
+          <t>임의 슬라이더로 침수면을 움직인 장면을 예측이라고 부르지 않는다.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -3993,13 +4225,13 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>전파 대상·지역·매체·문안 확인</t>
+          <t>예측과 영향 근거를 실제 결정, 승인, 전파·시설 요청과 결과로 연결한다.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4017,13 +4249,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>판단 요약</t>
+        </is>
+      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>시설 운영·점검 요청 승인</t>
+          <t>IA-02에서 확정한 위험판단과 영향, 불확실성·반대 근거의 대응용 요약</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4041,13 +4277,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>권고</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>실패 건 재시도 또는 대체조치 기록</t>
+          <t>권고 대응수준, 대상, 시점, 생성 근거</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4065,13 +4305,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>SOP 초안</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>사건을 대응중 또는 통제로 전환</t>
+          <t>단계별 업무, 담당 조직, 자동/승인 구분</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4089,13 +4333,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>시스템은 권고·SOP·전파문·보고서 초안을 만들 수 있다.</t>
+          <t>선택안, 수정사항, 승인자·시각·사유</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4113,13 +4361,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>사건 확정, 대응수준, 외부 전파와 시설 요청은 담당자가 승인한다.</t>
+          <t>전파(CAP 1.2 필드 구조)·도로통제·시설점검·운영 요청</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4137,13 +4389,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>실제 원격제어가 확인되지 않으면 요청·승인·결과 확인까지만 표현한다.</t>
+          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4161,13 +4417,13 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>실행 실패를 성공으로 덮어쓰지 않고 실패와 대체조치를 각각 기록한다.</t>
+          <t>권고 검토·수정·기각</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4175,23 +4431,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>사건 진행과 판단 근거를 재구성하고 예측·대응의 실제 결과를 검토한다.</t>
+          <t>SOP 항목 선택 및 담당 배정</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4199,27 +4455,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>사건 타임라인</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>원천 이벤트, 사건 상태, 예측판, 결정, 실행과 현장 결과</t>
+          <t>전파 대상·지역·매체·문안 확인</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4227,27 +4479,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>주요 시간</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>최초 감지·후보 생성·확인·전파·조치·통제·종료</t>
+          <t>시설 운영·점검 요청 승인</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4255,27 +4503,23 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>예측 검증</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>예측 대 실제, 과대·과소, 비교 불가 사유</t>
+          <t>실패 건 재시도 또는 대체조치 기록</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4283,27 +4527,23 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>대응 검토</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소와 소요시간</t>
+          <t>사건을 대응중 또는 통제로 전환</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -4311,27 +4551,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>보고서</t>
-        </is>
-      </c>
+          <t>승인 경계</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 초안, 근거 링크, 담당자 수정·확정</t>
+          <t>시스템은 권고·SOP·전파문·보고서 초안을 만들 수 있다.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -4339,27 +4575,23 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>개선 항목</t>
-        </is>
-      </c>
+          <t>승인 경계</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>임계치·모델·데이터·SOP 검토 과제</t>
+          <t>사건 확정, 대응수준, 외부 전파와 시설 요청은 담당자가 승인한다.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -4367,23 +4599,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>사건 종료 또는 재개</t>
+          <t>실제 원격제어가 확인되지 않으면 요청·승인·결과 확인까지만 표현한다.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -4391,23 +4623,23 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>예측판과 실제 관측 비교</t>
+          <t>실행 실패를 성공으로 덮어쓰지 않고 실패와 대체조치를 각각 기록한다.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -4425,13 +4657,13 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>누락 근거·결과 보완 요청</t>
+          <t>사건 진행과 판단 근거를 재구성하고 예측·대응의 실제 결과를 검토한다.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -4449,13 +4681,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>사건 타임라인</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 생성·수정·확정·내보내기</t>
+          <t>원천 이벤트, 사건 상태, 예측판, 결정, 실행과 현장 결과</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -4473,13 +4709,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>주요 시간</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>후속 개선 항목 등록</t>
+          <t>최초 감지·후보 생성·확인·전파·조치·통제·종료</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -4497,13 +4737,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>예측 검증</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>이 사건의 대응 이력으로 대응 모의훈련 시나리오 후보 생성 요청. 편집·실행은 IA-A01 범위</t>
+          <t>예측 대 실제, 과대·과소, 비교 불가 사유</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -4521,13 +4765,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>대응 검토</t>
+        </is>
+      </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>보고서는 독립된 대메뉴에서 새로 시작하는 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다.</t>
+          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소와 소요시간</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -4535,23 +4783,27 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>보고서</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
+          <t>상황보고서 초안, 근거 링크, 담당자 수정·확정</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -4559,23 +4811,27 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>개선 항목</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>현재 사건 요약과 누락 정보 안내</t>
+          <t>임계치·모델·데이터·SOP 검토 과제</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -4583,23 +4839,23 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+          <t>사건 종료 또는 재개</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -4607,23 +4863,23 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>유사 사건·과거 결정 탐색</t>
+          <t>예측판과 실제 관측 비교</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -4631,23 +4887,23 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>전파문·상황보고서 초안 작성</t>
+          <t>누락 근거·결과 보완 요청</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -4655,23 +4911,23 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+          <t>상황보고서 생성·수정·확정·내보내기</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -4679,23 +4935,23 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>원천에 없는 사실 생성 금지</t>
+          <t>후속 개선 항목 등록</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -4703,23 +4959,23 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>확실성·한계를 숨긴 단정 금지</t>
+          <t>이 사건의 대응 이력으로 대응 모의훈련 시나리오 후보 생성 요청. 목록·실행은 선택 에필로그 IA-T01, 편집·예약과 C 유형 훈련은 후속 범위</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -4727,23 +4983,23 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>담당자 승인 대행 금지</t>
+          <t>보고서는 독립된 대메뉴에서 새로 시작하는 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -4761,13 +5017,13 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -4775,19 +5031,23 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr"/>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
+          <t>현재 사건 요약과 누락 정보 안내</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -4795,190 +5055,402 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>데이터 연계</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>원천·주기·권한·상태·스키마 관리</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>임계치·규칙</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>지점·유형별 기준, 변화율, 사건 연결 규칙</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>유사 사건·과거 결정 탐색</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>전파문·상황보고서 초안 작성</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>전파 대상</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>부서·기관·지역·매체·권한</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·입출력·유효시간·검증상태</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>원천에 없는 사실 생성 금지</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>사용자·권한</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>역할, 승인권한, 개인정보 접근</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>후속 제품 범위</t>
-        </is>
-      </c>
+          <t>확실성·한계를 숨긴 단정 금지</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr"/>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
+          <t>담당자 승인 대행 금지</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr"/>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr"/>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>데이터 연계</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>원천·주기·권한·상태·스키마 관리</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>임계치·규칙</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>지점·유형별 기준, 변화율, 사건 연결 규칙</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr"/>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>전파 대상</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>부서·기관·지역·매체·권한</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>모델·버전·입출력·유효시간·검증상태</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>사용자·권한</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>역할, 승인권한, 개인정보 접근</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>후속 제품 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
           <t>관리 화면 수는 대표 데모 성과에 포함하지 않는다.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5062,7 +5534,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>계약과 미확보 조건</t>
+          <t>Phase 1 서항 자산과 시나리오 Forecast로 시간 조절·대안 선택이 동작하는 예측 화면. 계산 주체·교체 대상은 내부 관리</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5546,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>화선·플룸·풍하측 영향면</t>
+          <t>화선·연기·풍하측 영향면</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5094,7 +5566,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>정적 개념 예시</t>
+          <t>정적 개념 예시. 대표 사례 산불</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5173,6 +5645,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5188,7 +5661,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>업무 공간</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -5199,6 +5672,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>주요 행위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>기준 라우트</t>
         </is>
       </c>
     </row>
@@ -5228,6 +5706,11 @@
           <t>감시 우선대상 선택</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>/incidents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5255,6 +5738,11 @@
           <t>큐에 나타난 후보를 열고 연결 근거 확인</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>/incidents → /incidents/:incidentId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5282,6 +5770,11 @@
           <t>영상 확인·사건 확정</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5309,6 +5802,11 @@
           <t>위험·완화·불확실성 검토</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5323,7 +5821,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IA-03 트윈 비교</t>
+          <t>IA-02 → IA-03 디지털트윈</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -5333,7 +5831,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>기준 전망 선택</t>
+          <t>근거 목록의 예측 이벤트를 눌러 지도를 디지털트윈 화면으로</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/twin?forecastId=...</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5853,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>IA-03 트윈 비교</t>
+          <t>IA-03 디지털트윈</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -5360,7 +5863,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>가능한 대안 비교</t>
+          <t>대안 선택으로 기준 대 대안 비교, [이 전망으로 대응 검토]</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/twin?forecastId=...&amp;alternativeId=...</t>
         </is>
       </c>
     </row>
@@ -5390,6 +5898,11 @@
           <t>SOP·전파·시설 요청 승인</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/response</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5417,6 +5930,11 @@
           <t>실패·대체조치 기록</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>/incidents/:incidentId/response</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5442,6 +5960,11 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>종료·검증·보고서</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>/records/:incidentId</t>
         </is>
       </c>
     </row>
@@ -5455,6 +5978,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5467,7 +5991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5607,8 +6131,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>scenarioId</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>D8에서 생성한 훈련 시나리오와 원 사건 스냅샷 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>trainingRunId</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>같은 시나리오의 개별 훈련 실행·결정·결과 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>화면이 각자 사건 상태와 시간을 복제해서 소유하지 않는다.</t>
         </is>
@@ -5625,7 +6173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5872,9 +6420,43 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TrainingScenario</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>IA-05·IA-T01</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>원 사건 스냅샷·이벤트·Forecast·대응 이력 참조, 훈련 조건·목표·버전</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TrainingRun</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>IA-T01</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>시나리오별 실행상태·참여자·훈련 결정·조치·결과·회고</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>같은 객체를 화면마다 다른 값으로 복제하지 않고, 질문에 맞는 요약만 다르게 보여준다.</t>
         </is>
@@ -5973,12 +6555,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>실데이터·표본·합성 혼합</t>
+          <t>실데이터·표본·시나리오 혼합</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>사건의 scenarioMode, 이벤트별 dataOrigin·ingestionMode와 기준시각 표시</t>
+          <t>같은 제품 UI를 사용하고 원본시각·시나리오시각·dataOrigin·ingestionMode는 내부 계약에서 유지</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6203,7 +6785,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-03 디지털트윈(사건 지도 안) · IA-T01 훈련 실행 화면</t>
         </is>
       </c>
     </row>
@@ -6220,65 +6802,65 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>IA-03 공통 다섯 영역</t>
+          <t>IA-03 구성 요소</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>폭염 전용 지구본</t>
+          <t>사전 모의분석(drill) 모드</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재편</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>03_유형별디지털트윈.md의 E 대기·면 노출 장기 후보</t>
+          <t>IA-T01 대응 모의훈련의 실행 화면. 이름은 사전 조건분석</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>대응 팝업·위험도·권고·SOP</t>
+          <t>폭염 전용 지구본</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>통합</t>
+          <t>제외</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>03_유형별디지털트윈.md의 E 대기·면 노출 장기 후보</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>실행 결과·사건 타임라인</t>
+          <t>대응 팝업·위험도·권고·SOP</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>재편</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IA-04 결과·IA-05 기록</t>
+          <t>IA-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>통계·분석</t>
+          <t>실행 결과·사건 타임라인</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -6288,31 +6870,31 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IA-05 기록·검증</t>
+          <t>IA-04 결과·IA-05 기록</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>보고서 생성·조회</t>
+          <t>통계·분석</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>재편</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IA-05 산출물로 통합 검토</t>
+          <t>IA-05 기록·검증</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AI 검색 페이지</t>
+          <t>보고서 생성·조회</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -6322,39 +6904,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IA-G01 공통 보조로 통합 검토</t>
+          <t>IA-05 산출물로 통합 검토</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>전 지구 위험도 표</t>
+          <t>AI 검색 페이지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>후속 제품 분석 범위</t>
+          <t>IA-G01 공통 보조로 통합 검토</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>전 지구 위험도 표</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>후속 제품 분석 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>전파·SOP·임계치 관리</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>IA-A01</t>
         </is>

--- a/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
+++ b/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-11 11:52 생성). 값이 갈리면 md 가 이긴다</t>
+          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-14 11:55 생성). 값이 갈리면 md 가 이긴다</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>담당자가 하나의 사건을 발견하고, 근거를 확인하고, 미래 영향을 비교하고, 대응을 실행한 뒤 결과를 검증하는 흐름을 끊김 없이 지원하는 구조를 정의한다.</t>
+          <t>센서·API·VLM과 디지털트윈 예측을 결합해 담당자가 확인할 알림과 사건 후보를 만들고, 근거 확인부터 SOP 대응·실행·보고서까지 끊김 없이 이어지는 구조를 정의한다.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>서로 다른 이벤트의 시간·공간·의미 연결 근거</t>
+          <t>센서·API·VLM·Forecast의 단일·복합 조건으로 생성된 알림과 사건 후보 연결 이유</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>담당자 사건 확인과 상태 전환</t>
+          <t>서로 다른 이벤트의 시간·공간·의미 연결 근거</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>현재 상태와 기준 전망 분리</t>
+          <t>담당자 사건 확인과 상태 전환</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>영향 근거를 대응안·전파·조치에 연결</t>
+          <t>현재 상태와 기준 전망 분리</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>승인과 시스템 권고 분리</t>
+          <t>영향 근거를 대응안·전파·조치에 연결</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>실패·미응답·대체조치 기록</t>
+          <t>승인과 시스템 권고 분리</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>사건 타임라인과 결과 기록</t>
+          <t>실패·미응답·대체조치 기록</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>관측·갱신시각, 품질, 출처기관과 예측 기준시각·모델 등 제품에 필요한 근거 표시</t>
+          <t>사건 타임라인과 결과 기록</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>특보 헤더와 전파문의 CAP 1.2 필드 구조</t>
+          <t>관측·갱신시각, 품질, 출처기관과 예측 기준시각·모델 등 제품에 필요한 근거 표시</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>예측 이벤트를 누르면 사건 지도가 디지털트윈 화면으로 바뀌는 흐름과 대안 선택</t>
+          <t>특보 헤더와 전파문의 CAP 1.2 필드 구조</t>
         </is>
       </c>
     </row>
@@ -1108,31 +1108,31 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D8의 대응 모의훈련 진입점. A 시나리오 목록·실행은 일정이 허용할 때 선택 에필로그로 구현하고 편집·예약과 C 훈련은 제외</t>
+          <t>다지표 가중 위험도 매트릭스의 등급·지표별 기여도와 이를 설명하는 4축</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
+          <t>§18 Phase 2 데모 범위 · 데모 구현 시 반드시 포함할 핵심</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>A 대응 모의훈련 목록·실행 에필로그. 편집·예약과 C 유형 훈련은 후속 범위</t>
+          <t>예측 이벤트를 누르면 사건 지도가 디지털트윈 화면으로 바뀌는 흐름과 대안 선택</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
+          <t>§18 Phase 2 데모 범위 · 데모 구현 시 반드시 포함할 핵심</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C 해안 월류의 시나리오 Forecast 기반 모의 예측 화면(R1)</t>
+          <t>D8의 대응 모의훈련 진입점. A 시나리오 목록·실행은 일정이 허용할 때 선택 에필로그로 구현하고 편집·예약과 C 훈련은 제외</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D 산불·F 지반의 정적 개념 예시(R0)</t>
+          <t>A 대응 모의훈련 목록·실행 에필로그. 편집·예약과 C 유형 훈련은 후속 범위</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>G 펌프 장애가 독립 고장 기준을 넘을 때 별도 사건으로 분리되는 관계 표시</t>
+          <t>C 해안 월류의 시나리오 Forecast 기반 모의 예측 화면(R1)</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>기록·검증 정리, 사건 AI 보조 오버레이와 운영 관리 보조 구조</t>
+          <t>D 산불·F 지반의 정적 개념 예시(R0)</t>
         </is>
       </c>
     </row>
@@ -1180,31 +1180,31 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C 모의 예측과 G 파생 장면은 제품 방향에는 포함하되 대표 도시침수 D0~D8의 완료 조건에는 넣지 않는다. 항목별 일정과 시연 효과를 확인해 I4에서 선택한다.</t>
+          <t>G 펌프 장애가 독립 고장 기준을 넘을 때 별도 사건으로 분리되는 관계 표시</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
+          <t>기록·검증 정리, 사건 AI 보조 오버레이와 운영 관리 보조 구조</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>기준·대안 예측판 비교</t>
+          <t>C 모의 예측과 G 파생 장면은 제품 방향에는 포함하되 대표 도시침수 D0~D8의 완료 조건에는 넣지 않는다. 항목별 일정과 시연 효과를 확인해 I4에서 선택한다.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>영향 대상과 실제 SOP·전파문 연결</t>
+          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>예측과 실제 관측의 오차 검증</t>
+          <t>기준·대안 예측판 비교</t>
         </is>
       </c>
     </row>
@@ -1240,31 +1240,31 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 디지털트윈 화면은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하며 기본 제품 UI에 제작 설명을 노출하지 않는다. 검증되지 않은 모델 성능이나 실제 운영 성과로 대외 주장하지 않는다.</t>
+          <t>영향 대상과 실제 SOP·전파문 연결</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>모든 유형의 동적 모델</t>
+          <t>예측과 실제 관측의 오차 검증</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>실제 재난문자·시설 원격제어</t>
+          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 디지털트윈 화면은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하며 기본 제품 UI에 제작 설명을 노출하지 않는다. 검증되지 않은 모델 성능이나 실제 운영 성과로 대외 주장하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
+          <t>모든 유형의 동적 모델</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련 시나리오 편집·예약과 C 유형 훈련. A 목록·실행은 선택 에필로그 IA-T01</t>
+          <t>실제 재난문자·시설 원격제어</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>대규모 운영 통계와 SLA</t>
+          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
         </is>
       </c>
     </row>
@@ -1312,31 +1312,31 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
+          <t>대응 모의훈련 시나리오 편집·예약과 C 유형 훈련. A 목록·실행은 선택 에필로그 IA-T01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
+          <t>대규모 운영 통계와 SLA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>답할 사용자 질문</t>
+          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>사용하는 공통 객체와 필드</t>
+          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>진입 조건과 다음 행동</t>
+          <t>답할 사용자 질문</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>시스템 생성 정보와 담당자 결정의 구분</t>
+          <t>사용하는 공통 객체와 필드</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>정상·빈·지연·결측·실패 상태와 내부 시나리오 처리</t>
+          <t>진입 조건과 다음 행동</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>데이터·모델·업무 근거와 준비도</t>
+          <t>시스템 생성 정보와 담당자 결정의 구분</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>대표 데모 포함 여부</t>
+          <t>정상·빈·지연·결측·실패 상태와 내부 시나리오 처리</t>
         </is>
       </c>
     </row>
@@ -1420,31 +1420,31 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>기존 자산의 재사용·재편·제외 판정</t>
+          <t>데이터·모델·업무 근거와 준비도</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>다음은 현재 기준안에서 결정됐다.</t>
+          <t>대표 데모 포함 여부</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 사건 우선 큐에 나타나면 IA-02로 연다.</t>
+          <t>기존 자산의 재사용·재편·제외 판정</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
+          <t>다음은 현재 기준안에서 결정됐다.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다.</t>
+          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 사건 우선 큐에 나타나면 IA-02로 연다.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>P0 자료 확인 전 IA-03은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하고, 기본 제품 UI에 제작 설명을 넣지 않는다.</t>
+          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>IA-02는 Phase 1 지구 재난관제 팝업의 개요 고정·탭 골조를 유지하고 내용을 사건 개요·근거·영상·관계 이력 중심으로 재편한다.</t>
+          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>IA-03 디지털트윈은 독립 페이지가 아니라 사건 작업공간 안에서 예측 이벤트를 눌러 여는 디지털트윈 화면이다. IA-04 대응은 사건 화면 안 팝업으로 둔다. (2026-09-10 저녁 변경. 이전 결정은 독립 페이지)</t>
+          <t>P0 자료 확인 전 IA-03은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하고, 기본 제품 UI에 제작 설명을 넣지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>IA-05는 상시 접근 가능한 독립 페이지로 두되 대표 데모의 주 동선에서는 D8에 진입한다.</t>
+          <t>IA-02는 Phase 1 지구 재난관제와 좌우 패널 골조를 지도 중심 사건 작업공간으로 재편한다. 좌측은 선택한 알림·사건의 관련 이벤트 현황, 우측은 판단·전망과 대응 결과 요약이며 사건 범위는 지점부터 도시 전역까지 수용한다.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C·D·F 비교는 IA-03 유형 전환으로 설계한다. C 모의 예측과 R0인 D·F 정적 개념 예시는 I4 선택 범위다.</t>
+          <t>IA-03 디지털트윈은 독립 페이지가 아니라 사건 작업공간 안에서 예측 이벤트를 눌러 여는 디지털트윈 화면이다. IA-04 대응 승인·실행은 사건 위의 집중 팝업으로 분리한다. 화면 배치와 전환은 04 정본을 따른다.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>G 파생 관계 표시도 I4 선택 범위다. 대표 데모 필수 범위는 도시침수 D0~D8과 D8의 TrainingScenario 생성 진입점·전달 계약까지다.</t>
+          <t>IA-05는 상시 접근 가능한 독립 페이지로 두되 대표 데모의 주 동선에서는 D8에 진입한다.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련은 사이드바 메뉴(IA-T01)로 설계한다. D8 진입점은 포함하고, 일정이 허용하면 A 시나리오 목록과 실행을 선택 에필로그로 만든다. 편집·예약과 C 유형 훈련은 후속 범위다. 실행 화면은 Phase 1 트윈 페이지를 사전 조건분석으로 쓰며 IA-05의 대응 이력이 시나리오의 입력이 된다.</t>
+          <t>C·D·F 비교는 IA-03 유형 전환으로 설계한다. C 모의 예측과 R0인 D·F 정적 개념 예시는 I4 선택 범위다.</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>남은 확인은 다음 두 가지다.</t>
+          <t>G 파생 관계 표시도 I4 선택 범위다. 대표 데모 필수 범위는 도시침수 D0~D8과 D8의 TrainingScenario 생성 진입점·전달 계약까지다.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>선택 에필로그를 구현할 경우 D8 원 사건에서 IA-T01 훈련 시나리오를 생성할 입력·참조 ID 계약을 구현 설계에서 확정한다.</t>
+          <t>대응 모의훈련은 사이드바 메뉴(IA-T01)로 설계한다. D8 진입점은 포함하고, 일정이 허용하면 A 시나리오 목록과 실행을 선택 에필로그로 만든다. 편집·예약과 C 유형 훈련은 후속 범위다. 실행 화면은 Phase 1 트윈 페이지를 사전 조건분석으로 쓰며 IA-05의 대응 이력이 시나리오의 입력이 된다.</t>
         </is>
       </c>
     </row>
@@ -1587,6 +1587,30 @@
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>남은 확인은 다음 두 가지다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>선택 에필로그를 구현할 경우 D8 원 사건에서 IA-T01 훈련 시나리오를 생성할 입력·참조 ID 계약을 구현 설계에서 확정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>실제 기관의 메뉴 권한과 운영 절차를 확인해 IA-05 상시 접근 권한과 훈련 관리 책임 조직을 정한다. 이번 데모에서는 확정하지 않고 추후 제품 개발 시 정의한다.</t>
         </is>
@@ -1688,7 +1712,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>/incidents</t>
+          <t>/scr-01</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1698,7 +1722,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>감시 우선대상·사건·후보 목록</t>
+          <t>감시 우선대상·복합 알림·사건·후보 목록</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1709,12 +1733,12 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>업무 시작 또는 D0 감시 우선대상 갱신</t>
+          <t>업무 시작, D0 감시 우선대상 또는 복합 알림 갱신</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>감시 대상 확인, D1 후보가 생기면 사건 열기</t>
+          <t>알림 근거 확인, D1 후보가 생기면 사건 열기</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1760,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1757,7 +1781,7 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>후보 선택, 관련 사건 링크 또는 검토 요청</t>
+          <t>복합 알림·후보 선택, 관련 사건 링크 또는 검토 요청</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1784,7 +1808,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/twin</t>
+          <t>/scr-05/:districtId</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1827,12 +1851,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사건 맥락을 유지하는 팝업·패널</t>
+          <t>사건 작업공간 위의 집중 팝업</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/response</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1880,7 +1904,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>/records, /records/:incidentId</t>
+          <t>/scr-04, /scr-07?event=...</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1928,7 +1952,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>/drills, /drills/:scenarioId/run</t>
+          <t>/scr-05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1976,7 +2000,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>별도 라우트 없음</t>
+          <t>/scr-06</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2016,7 +2040,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>/admin/*</t>
+          <t>추후 정의</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2065,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2182,17 +2206,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>사건 우선 큐</t>
+          <t>복합 알림</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·확인됨·대응중·통제 사건, 긴급도, 심각도, 확실성, 경과시간</t>
+          <t>센서·API·VLM·Forecast의 단일 심각 또는 복합 조건, 알림 등급·상태·연결 이유</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>AttentionAlert·Event·Forecast</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2238,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>후보 근거</t>
+          <t>사건 우선 큐</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>최초 징후, 연결 이벤트 수가 아닌 근거 종류, 추가 확인 필요사항</t>
+          <t>후보·확인중·확인됨·대응중·통제 사건, 매트릭스 위험등급, 긴급도, 확실성, 경과시간</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Event·Incident</t>
+          <t>Incident</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2270,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>공간 개요</t>
+          <t>후보 근거</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>현재·예상 영향권, 원인·파생 사건, 데이터 장애 위치</t>
+          <t>최초 징후, 연결 이벤트 수가 아닌 근거 종류, 추가 확인 필요사항</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Incident·AffectedArea</t>
+          <t>Event·Incident</t>
         </is>
       </c>
     </row>
@@ -2278,17 +2302,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>광역 맥락</t>
+          <t>공간 개요</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>특보, 예측 변화, 도시 대응단계</t>
+          <t>현재·예상 영향권, 원인·파생 사건, 데이터 장애 위치</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Event·Forecast·CityOperationalState</t>
+          <t>Incident·AffectedArea</t>
         </is>
       </c>
     </row>
@@ -2310,17 +2334,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>데이터 상태</t>
+          <t>광역 맥락</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>지연·결측·의심 원천과 영향받는 사건</t>
+          <t>특보, 예측 변화, 도시 대응단계</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Event·Incident</t>
+          <t>Event·Forecast·CityOperationalState</t>
         </is>
       </c>
     </row>
@@ -2337,16 +2361,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>필수 정보</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>데이터 상태</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>감시 우선대상 또는 사건·사건 후보 열기</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t>지연·결측·의심 원천과 영향받는 사건</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Event·Incident</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2367,7 +2399,7 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>담당자·상태·유형으로 우선 큐 필터링</t>
+          <t>감시 우선대상 또는 사건·사건 후보 열기</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -2391,7 +2423,7 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>데이터 장애가 영향을 주는 사건 확인</t>
+          <t>담당자·상태·유형으로 우선 큐 필터링</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2415,7 +2447,7 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>원인·파생 사건 묶음 펼치기</t>
+          <t>데이터 장애가 영향을 주는 사건 확인</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -2433,13 +2465,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>제외할 구성</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>지구 수와 사건 수를 같은 방식으로 집계한 도넛</t>
+          <t>원인·파생 사건 묶음 펼치기</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -2463,7 +2495,7 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>모든 센서값을 동일 우선순위로 나열한 현황판</t>
+          <t>지구 수와 사건 수를 같은 방식으로 집계한 도넛</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -2487,7 +2519,7 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>사건과 무관한 기상정보를 큰 카드로 고정 배치</t>
+          <t>모든 센서값을 동일 우선순위로 나열한 현황판</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -2511,7 +2543,7 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>전 지구 × 전 지표 신호등 표를 첫 화면의 중심으로 사용</t>
+          <t>사건과 무관한 기상정보를 큰 카드로 고정 배치</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -2519,23 +2551,23 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IA-02</t>
+          <t>IA-01</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>사건 작업공간</t>
+          <t>종합상황</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>제외할 구성</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>사건 후보가 왜 만들어졌는지 확인하고, 담당자가 실제 사건 여부와 관계를 결정하는 중심 화면이다.</t>
+          <t>전 지구 × 전 지표 신호등 표를 첫 화면의 중심으로 사용</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -2553,17 +2585,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>공통 헤더</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>사건 식별</t>
-        </is>
-      </c>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>사건 ID, 제목, 재난유형, 공간 범위</t>
+          <t>사건 후보가 왜 만들어졌는지 확인하고, 담당자가 실제 사건 여부와 관계를 결정하는 중심 화면이다. 사건 작업공간은 특정 현장 하나를 뜻하지 않는다. 사건의 scope에 따라 지점·시설·구역·지구·도시 전역을 같은 구조로 다루며 지도 범위와 정보 밀도가 함께 바뀐다.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -2581,17 +2609,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>공통 헤더</t>
+          <t>기본 화면 구조</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>처리 상태</t>
+          <t>중심 지도</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·확인됨·대응중·통제·종료·오탐·병합됨</t>
+          <t>사건의 실제·예상 영향 범위와 센서·CCTV·시설·이벤트 발생 위치를 공간으로 표시</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -2609,17 +2637,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>공통 헤더</t>
+          <t>기본 화면 구조</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>위험 판단</t>
+          <t>좌측 관련 이벤트 현황</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>심각도·긴급도·확실성·추세를 독립 표시</t>
+          <t>선택한 복합 알림 또는 사건과 연결된 관측·특보·VLM·시설·Forecast·품질 이벤트를 시간순으로 표시</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -2637,17 +2665,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>공통 헤더</t>
+          <t>기본 화면 구조</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>우측 판단·전망</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>최초 관측, 사건 생성, 최신 갱신, 경과시간</t>
+          <t>위험도 매트릭스와 현재 판단·전망, 승인 뒤 대응 결과 요약과 실행 진입</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -2665,17 +2693,13 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>공통 헤더</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
+          <t>기본 화면 구조</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>담당 조직·담당자·인계 상태</t>
+          <t>사건 생성 전에는 선택한 복합 알림을 구성한 이벤트를, 사건 생성 후에는 해당 Incident에 연결된 이벤트· 판단·예측·조치를 보여준다. 같은 지구에서 발생했어도 현재 사건과 연결되지 않은 이벤트는 별도 지구 현황으로 구분한다. 이벤트를 선택하면 지도 위치와 근거 상세가 함께 바뀌고, Forecast 이벤트를 선택하면 같은 지도가 디지털트윈 예측 모드로 전환된다.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -2698,12 +2722,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>운영 근거</t>
+          <t>사건 식별</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>관측·갱신시각, 품질, 출처기관, 예측 기준시각·모델 등 실제 판단에 필요한 정보</t>
+          <t>사건 ID, 제목, 재난유형, 공간 범위</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -2721,17 +2745,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>공통 헤더</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>사건 개요</t>
+          <t>처리 상태</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>현재 상황 한 문장 요약</t>
+          <t>후보·확인중·확인됨·대응중·통제·종료·오탐·병합됨</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -2749,17 +2773,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>공통 헤더</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>사건 개요</t>
+          <t>위험 판단</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>원인·악화·완화 요인</t>
+          <t>심각도·긴급도·확실성·추세를 독립 표시</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -2777,17 +2801,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>공통 헤더</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>사건 개요</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>심각도·긴급도·확실성·추세와 반대 근거·불확실성·누락정보</t>
+          <t>최초 관측, 사건 생성, 최신 갱신, 경과시간</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2805,17 +2829,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>공통 헤더</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>사건 개요</t>
+          <t>담당</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>실제·예상 영향 공간</t>
+          <t>담당 조직·담당자·인계 상태</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -2833,17 +2857,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>공통 헤더</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>사건 개요</t>
+          <t>운영 근거</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>원인·파생·동시 사건 관계</t>
+          <t>관측·갱신시각, 품질, 출처기관, 예측 기준시각·모델 등 실제 판단에 필요한 정보</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -2871,7 +2895,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>다음 확인 또는 결정이 필요한 항목</t>
+          <t>현재 상황 한 문장 요약</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -2894,12 +2918,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>강우·수위·조위·시설 등 시간 정렬</t>
+          <t>원인·악화·완화 요인</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -2922,12 +2946,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>원천 관측과 임계치·변화율 파생 결과 분리</t>
+          <t>위험도 매트릭스의 등급·점수·지표별 기여도와 이를 설명하는 심각도·긴급도·확실성·추세</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -2950,12 +2974,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>관측시각과 수신시각</t>
+          <t>위험·완화·반대 근거와 불확실성·누락정보</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2978,12 +3002,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>결측·지연·의심·보정 상태</t>
+          <t>실제·예상 영향 공간</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -3006,12 +3030,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>사건에 연결된 이유</t>
+          <t>원인·파생·동시 사건 관계</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -3034,12 +3058,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>관측 근거</t>
+          <t>사건 개요</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>침수예측판 갱신(E8)을 관측·영상과 같은 급의 근거로. 유효 시각·침수심·영향 요약 한 줄과 [디지털트윈 보기]</t>
+          <t>다음 확인 또는 결정이 필요한 항목</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -3062,12 +3086,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>영상·현장</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>사건 주변 CCTV와 선택 영상</t>
+          <t>강우·수위·조위·시설 등 시간 정렬</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -3090,12 +3114,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>영상·현장</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>VLM 분석 문장, 신뢰도, 모델·버전·분석시각</t>
+          <t>원천 관측과 임계치·변화율 파생 결과 분리</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -3118,12 +3142,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>영상·현장</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>실제 영상과 분석 결과 병렬 확인</t>
+          <t>관측시각과 수신시각</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -3146,12 +3170,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>영상·현장</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>현장 보고·사진·통행 가능 여부</t>
+          <t>결측·지연·의심·보정 상태</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -3174,12 +3198,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>상태·관계 이력</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>후보 생성·확인·오탐·병합·분리 기록</t>
+          <t>사건에 연결된 이유</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -3202,12 +3226,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>상태·관계 이력</t>
+          <t>관측 근거</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>상태 변경 사유와 담당자</t>
+          <t>침수예측판 갱신(E8)을 관측·영상과 같은 급의 근거로. 유효 시각·침수심·영향 요약 한 줄과 [디지털트윈 보기]</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -3230,12 +3254,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>상태·관계 이력</t>
+          <t>관련 이벤트 현황</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>외부 기관 사건과의 관계</t>
+          <t>현재 알림·사건에 연결된 이벤트를 시간순으로 표시</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3258,12 +3282,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>상태·관계 이력</t>
+          <t>관련 이벤트 현황</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>타임라인에 예측 유효 시각의 미래 눈금</t>
+          <t>이벤트 종류, 발생·갱신시각, 위치, 품질, 연결 이유와 확인 필요 여부 표시</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -3281,13 +3305,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>관련 이벤트 현황</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>확인, 추가 확인, 오탐</t>
+          <t>수위·강우·특보·VLM·시설·Forecast·품질을 같은 목록에서 구분</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3305,13 +3333,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>관련 이벤트 현황</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>기존 사건에 병합 또는 별도 사건으로 분리</t>
+          <t>선택한 이벤트의 센서·CCTV·시설·영향 범위를 지도에서 강조</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -3329,13 +3361,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>관련 이벤트 현황</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원인·파생·동시발생 관계 지정</t>
+          <t>같은 지구의 미연결 이벤트는 기본 목록과 섞지 않고 별도 현황으로 구분</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -3353,13 +3389,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>영상·현장</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>이후 트윈·대응에서 유지할 관측·영상·분석 근거 선택</t>
+          <t>사건 주변 CCTV와 선택 영상</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -3377,13 +3417,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>영상·현장</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>예측 이벤트를 눌러 디지털트윈 열기. 같은 화면의 지도가 디지털트윈 화면으로 바뀐다</t>
+          <t>VLM 분석 문장, 신뢰도, 모델·버전·분석시각</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3401,13 +3445,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>영상·현장</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>대응 검토 시작</t>
+          <t>실제 영상과 분석 결과 병렬 확인</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3415,23 +3463,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>영상·현장</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>사건 작업공간 안의 디지털트윈 화면이다. 담당자가 근거 목록이나 타임라인의 예측 이벤트를 누르면 같은 지도가 그 시각의 3D 디지털트윈 화면으로 바뀐다. 독립 페이지가 아니다. 현재 상태와 미래 전망을 구분하고, 조건을 바꿨을 때 영향이 어떻게 달라지는지 비교한다. 대응 모의훈련(IA-T01)이 같은 디지털트윈 화면을 사건 없이 사용한다.</t>
+          <t>현장 보고·사진·통행 가능 여부</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3439,183 +3491,159 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
+          <t>내부 구성</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3D 지도</t>
+          <t>상태·관계 이력</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>지도가 3D로 전환되고 지형·건물 위에 시간대별 침수심과 영향 대상(도로·건물·대상자)이 표시된다</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>트윈 페이지 3D 씬. 수면 하나를 배수권역 단위 침수심으로, 영향 대상 표시 추가</t>
-        </is>
-      </c>
+          <t>후보 생성·확인·오탐·병합·분리 기록</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
+          <t>내부 구성</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>시간 조절</t>
+          <t>상태·관계 이력</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>예측 시각을 옮긴다. 눈금은 예측판 유효 시각, 남은 시간 표시</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>시간축 패널</t>
-        </is>
-      </c>
+          <t>상태 변경 사유와 담당자</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
+          <t>내부 구성</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>대안 선택</t>
+          <t>상태·관계 이력</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>그대로 / 도로 통제 / 배수 대응</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>신설</t>
-        </is>
-      </c>
+          <t>외부 기관 사건과의 관계</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
+          <t>내부 구성</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>영향 결과</t>
+          <t>상태·관계 이력</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>기준 전망과 대안 전망의 2열 비교</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>영향 결과 카드. 열 제목만 바뀜</t>
-        </is>
-      </c>
+          <t>타임라인에 예측 유효 시각의 미래 눈금</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>근거·한계</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·입력·기준시각·품질·가정</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>근거 카드에 항목 추가</t>
-        </is>
-      </c>
+          <t>확인, 추가 확인, 오탐</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>구성 요소</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>시연 시각 이후에 실제로 일어난 일은 눈금에 넣지 않는다. 판단에 쓰는 값은 눈금값이고 눈금 사이 값은 "사용자가 고른 시각"으로 구분한다.</t>
+          <t>기존 사건에 병합 또는 별도 사건으로 분리</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3623,130 +3651,98 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>현재 상태</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>지금 실제로 관측된 것은 무엇인가?</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>관측값·시설상태·영상·품질·기준시각</t>
-        </is>
-      </c>
+          <t>원인·파생·동시발생 관계 지정</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>기준 전망</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>현재 조건이 유지되면 어떻게 되는가?</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>유효시간별 공간 결과·도달시간·강도</t>
-        </is>
-      </c>
+          <t>이후 트윈·대응에서 유지할 관측·영상·분석 근거 선택</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>대안 전망</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>무엇을 바꾸었고 무엇이 달라지는가?</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>변경 조건·기준 대비 차이</t>
-        </is>
-      </c>
+          <t>예측 이벤트를 눌러 디지털트윈 열기. 같은 화면의 지도가 디지털트윈 화면으로 바뀐다</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IA-03</t>
+          <t>IA-02</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈</t>
+          <t>사건 작업공간</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>영향 결과</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>누가·어디가·언제 영향을 받는가?</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>도로·건물·시설·대상·노출·중단</t>
-        </is>
-      </c>
+          <t>대응 검토 시작</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3761,24 +3757,16 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>공통 다섯 영역</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>근거·한계</t>
-        </is>
-      </c>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>무엇으로 계산했고 어디까지 믿을 수 있는가?</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>모델·버전·입력·가정·불확실성·결측</t>
-        </is>
-      </c>
+          <t>사건 작업공간 안의 디지털트윈 화면이다. 담당자가 근거 목록이나 타임라인의 예측 이벤트를 누르면 같은 지도가 그 시각의 3D 디지털트윈 화면으로 바뀐다. 독립 페이지가 아니다. 현재 상태와 미래 전망을 구분하고, 조건을 바꿨을 때 영향이 어떻게 달라지는지 비교한다. 대응 모의훈련(IA-T01)이 같은 디지털트윈 화면을 사건 없이 사용한다.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3793,16 +3781,24 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>3D 지도</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>배수권역·관로망·센서·CCTV 위치</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>지도가 3D로 전환되고 지형·건물 위에 시간대별 침수심과 영향 대상(도로·건물·대상자)이 표시된다</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>트윈 페이지 3D 씬. 수면 하나를 배수권역 단위 침수심으로, 영향 대상 표시 추가</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3817,16 +3813,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>시간 조절</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>현재 강우·관로·도로수위·조위·펌프·저류시설 가용성</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
+          <t>예측 시각을 옮긴다. 눈금은 예측판 유효 시각, 남은 시간 표시</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>시간축 패널</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3841,16 +3845,24 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>대안 선택</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>시간대별 침수심·범위·도달시간</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>그대로 / 도로 통제 / 배수 대응</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>신설</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3865,16 +3877,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>기준 전망과, 데이터가 있을 때의 배수·통제 대안</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+          <t>기준 전망과 대안 전망의 2열 비교</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과 카드. 열 제목만 바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3889,16 +3909,24 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>구성 요소</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>근거·한계</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>도로·건물·중요시설·대상자 영향</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+          <t>모델·버전·입력·기준시각·품질·가정</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>근거 카드에 항목 추가</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3913,13 +3941,13 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>도시침수 대표 데모</t>
+          <t>구성 요소</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>외부 모델 수신인지 CUVIA 계산인지 구분</t>
+          <t>시연 시각 이후에 실제로 일어난 일은 눈금에 넣지 않는다. 판단에 쓰는 값은 눈금값이고 눈금 사이 값은 "사용자가 고른 시각"으로 구분한다.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3937,16 +3965,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>현재 상태</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>근거 목록·타임라인의 예측 이벤트 선택</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>지금 실제로 관측된 것은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>관측값·시설상태·영상·품질·기준시각</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3961,16 +3997,24 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>기준 전망</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>시간 조절로 유효 시각 이동</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>현재 조건이 유지되면 어떻게 되는가?</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>유효시간별 공간 결과·도달시간·강도</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3985,16 +4029,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>대안 전망</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>대안 선택(그대로 / 도로 통제 / 배수 대응)으로 기준 대 대안 비교</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
+          <t>무엇을 바꾸었고 무엇이 달라지는가?</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>변경 조건·기준 대비 차이</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4009,16 +4061,24 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>영향 결과</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>영향공간과 그 결과를 만든 근거 선택</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
+          <t>누가·어디가·언제 영향을 받는가?</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>도로·건물·시설·대상·노출·중단</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4033,16 +4093,24 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>공통 다섯 영역</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>근거·한계</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>[이 전망으로 대응 검토]: 선택한 시각·대안을 가지고 대응 팝업을 연다. 권고 카드에 전망 기준이 표시된다</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
+          <t>무엇으로 계산했고 어디까지 믿을 수 있는가?</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>모델·버전·입력·가정·불확실성·결측</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4057,13 +4125,13 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>긴급 시 디지털트윈 화면을 열지 않고 대응 검토로 갈 수 있다</t>
+          <t>배수권역·관로망·센서·CCTV 위치</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4081,13 +4149,13 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>유형별 교체 영역</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
+          <t>현재 강우·관로·도로수위·조위·펌프·저류시설 가용성</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4105,13 +4173,13 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>유형별 교체 영역</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
+          <t>시간대별 침수심·범위·도달시간</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4129,13 +4197,13 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>기준 전망이 없으면 예측을 가장하지 않고 필요한 모델·데이터를 표시한다.</t>
+          <t>기준 전망과, 데이터가 있을 때의 배수·통제 대안</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4153,13 +4221,13 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>지원하지 않는 대안은 대안 선택에 나타나지 않는다. 미지원·미실행·실패는 ModelRun 상태값으로만 기록하고 화면 라벨로 두지 않는다.</t>
+          <t>도로·건물·중요시설·대상자 영향</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4177,13 +4245,13 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>도시침수 대표 데모</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>실제 관측 비교가 없으면 검증 대기 상태와 필요한 결과를 표시한다.</t>
+          <t>외부 모델 수신인지 CUVIA 계산인지 구분</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4201,13 +4269,13 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>데이터가 없을 때</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>임의 슬라이더로 침수면을 움직인 장면을 예측이라고 부르지 않는다.</t>
+          <t>근거 목록·타임라인의 예측 이벤트 선택</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4215,23 +4283,23 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>예측과 영향 근거를 실제 결정, 승인, 전파·시설 요청과 결과로 연결한다.</t>
+          <t>시간 조절로 유효 시각 이동</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4239,27 +4307,23 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>판단 요약</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>IA-02에서 확정한 위험판단과 영향, 불확실성·반대 근거의 대응용 요약</t>
+          <t>대안 선택(그대로 / 도로 통제 / 배수 대응)으로 기준 대 대안 비교</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4267,27 +4331,23 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>권고</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>권고 대응수준, 대상, 시점, 생성 근거</t>
+          <t>영향공간과 그 결과를 만든 근거 선택</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4295,27 +4355,23 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>SOP 초안</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>단계별 업무, 담당 조직, 자동/승인 구분</t>
+          <t>[이 전망으로 대응 검토]: 선택한 시각·대안을 가지고 대응 집중 팝업을 연다. 권고 카드에 전망 기준이 표시된다</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4323,27 +4379,23 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>선택안, 수정사항, 승인자·시각·사유</t>
+          <t>긴급 시 디지털트윈 화면을 열지 않고 대응 검토로 갈 수 있다</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4351,27 +4403,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>실행</t>
-        </is>
-      </c>
+          <t>유형별 교체 영역</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>전파(CAP 1.2 필드 구조)·도로통제·시설점검·운영 요청</t>
+          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4379,27 +4427,23 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
+          <t>유형별 교체 영역</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소</t>
+          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4407,23 +4451,23 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>권고 검토·수정·기각</t>
+          <t>기준 전망이 없으면 예측을 가장하지 않고 필요한 모델·데이터를 표시한다.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4431,23 +4475,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>SOP 항목 선택 및 담당 배정</t>
+          <t>지원하지 않는 대안은 대안 선택에 나타나지 않는다. 미지원·미실행·실패는 ModelRun 상태값으로만 기록하고 화면 라벨로 두지 않는다.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4455,23 +4499,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>전파 대상·지역·매체·문안 확인</t>
+          <t>실제 관측 비교가 없으면 검증 대기 상태와 필요한 결과를 표시한다.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4479,23 +4523,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-03</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>대응·실행</t>
+          <t>디지털트윈</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>데이터가 없을 때</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>시설 운영·점검 요청 승인</t>
+          <t>임의 슬라이더로 침수면을 움직인 장면을 예측이라고 부르지 않는다.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4513,13 +4557,13 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>실패 건 재시도 또는 대체조치 기록</t>
+          <t>예측과 영향 근거를 실제 결정, 승인, 전파·시설 요청과 결과로 연결한다. 판단·전망은 사건 지도 위 우측 패널에서 확인하고, SOP·대응 승인·전파·조치 실행은 사건 맥락을 유지한 집중 팝업에서 처리한다. 팝업이 열리면 활성 조작면은 하나이며 닫은 뒤 결과는 우측 요약과 이력에 반영한다. 광역·복합 사건의 지역·기관·시설별 대응은 같은 실행 맥락 안에서 확장한다. 상세 배치는 04 정본을 따른다.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4537,13 +4581,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>판단 요약</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>사건을 대응중 또는 통제로 전환</t>
+          <t>IA-02에서 확인한 매트릭스 위험등급·기여 근거와 4축 설명, 영향·불확실성·반대 근거의 대응용 요약</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -4561,13 +4609,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>권고</t>
+        </is>
+      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>시스템은 권고·SOP·전파문·보고서 초안을 만들 수 있다.</t>
+          <t>권고 대응수준, 대상, 시점, 생성 근거</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -4585,13 +4637,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>SOP 초안</t>
+        </is>
+      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>사건 확정, 대응수준, 외부 전파와 시설 요청은 담당자가 승인한다.</t>
+          <t>단계별 업무, 담당 조직, 자동/승인 구분</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -4609,13 +4665,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>실제 원격제어가 확인되지 않으면 요청·승인·결과 확인까지만 표현한다.</t>
+          <t>선택안, 수정사항, 승인자·시각·사유</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -4633,13 +4693,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>승인 경계</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>실행 실패를 성공으로 덮어쓰지 않고 실패와 대체조치를 각각 기록한다.</t>
+          <t>전파(CAP 1.2 필드 구조)·도로통제·시설점검·운영 요청</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -4647,23 +4711,27 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>사건 진행과 판단 근거를 재구성하고 예측·대응의 실제 결과를 검토한다.</t>
+          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -4671,27 +4739,23 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>사건 타임라인</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>원천 이벤트, 사건 상태, 예측판, 결정, 실행과 현장 결과</t>
+          <t>권고 검토·수정·기각</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -4699,27 +4763,23 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>주요 시간</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>최초 감지·후보 생성·확인·전파·조치·통제·종료</t>
+          <t>SOP 항목 선택 및 담당 배정</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -4727,27 +4787,23 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>예측 검증</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>예측 대 실제, 과대·과소, 비교 불가 사유</t>
+          <t>전파 대상·지역·매체·문안 확인</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -4755,27 +4811,23 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>대응 검토</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소와 소요시간</t>
+          <t>시설 운영·점검 요청 승인</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -4783,27 +4835,23 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>보고서</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 초안, 근거 링크, 담당자 수정·확정</t>
+          <t>실패 건 재시도 또는 대체조치 기록</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -4811,27 +4859,23 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>개선 항목</t>
-        </is>
-      </c>
+          <t>주요 행동</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>임계치·모델·데이터·SOP 검토 과제</t>
+          <t>사건을 대응중 또는 통제로 전환</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -4839,23 +4883,23 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>사건 종료 또는 재개</t>
+          <t>시스템은 권고·SOP·전파문·보고서 초안을 만들 수 있다.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -4863,23 +4907,23 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>예측판과 실제 관측 비교</t>
+          <t>사건 확정, 대응수준, 외부 전파와 시설 요청은 담당자가 승인한다.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -4887,23 +4931,23 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>누락 근거·결과 보완 요청</t>
+          <t>실제 원격제어가 확인되지 않으면 요청·승인·결과 확인까지만 표현한다.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -4911,23 +4955,23 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>대응·실행</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>승인 경계</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 생성·수정·확정·내보내기</t>
+          <t>실행 실패를 성공으로 덮어쓰지 않고 실패와 대체조치를 각각 기록한다.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -4945,13 +4989,13 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>후속 개선 항목 등록</t>
+          <t>사건 진행과 판단 근거를 재구성하고 예측·대응의 실제 결과를 검토한다.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -4969,13 +5013,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>사건 타임라인</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>이 사건의 대응 이력으로 대응 모의훈련 시나리오 후보 생성 요청. 목록·실행은 선택 에필로그 IA-T01, 편집·예약과 C 유형 훈련은 후속 범위</t>
+          <t>원천 이벤트, 사건 상태, 예측판, 결정, 실행과 현장 결과</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -4993,13 +5041,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>주요 시간</t>
+        </is>
+      </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>보고서는 독립된 대메뉴에서 새로 시작하는 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다.</t>
+          <t>최초 감지·후보 생성·확인·전파·조치·통제·종료</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5007,23 +5059,27 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>예측 검증</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
+          <t>예측 대 실제, 과대·과소, 비교 불가 사유</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -5031,23 +5087,27 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>대응 검토</t>
+        </is>
+      </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>현재 사건 요약과 누락 정보 안내</t>
+          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소와 소요시간</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -5055,23 +5115,27 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>보고서</t>
+        </is>
+      </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+          <t>상황보고서 초안, 근거 링크, 담당자 수정·확정</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -5079,23 +5143,27 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>내부 구성</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>개선 항목</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>유사 사건·과거 결정 탐색</t>
+          <t>임계치·모델·데이터·SOP 검토 과제</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -5103,23 +5171,23 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>전파문·상황보고서 초안 작성</t>
+          <t>사건 종료 또는 재개</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -5127,23 +5195,23 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+          <t>예측판과 실제 관측 비교</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -5151,23 +5219,23 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>원천에 없는 사실 생성 금지</t>
+          <t>누락 근거·결과 보완 요청</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -5175,23 +5243,23 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>확실성·한계를 숨긴 단정 금지</t>
+          <t>상황보고서 생성·수정·확정·내보내기</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -5199,23 +5267,23 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>담당자 승인 대행 금지</t>
+          <t>후속 개선 항목 등록</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -5223,23 +5291,23 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>기록·검증</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>주요 행동</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+          <t>이 사건의 대응 이력으로 대응 모의훈련 시나리오 후보 생성 요청. 목록·실행은 선택 에필로그 IA-T01, 편집·예약과 C 유형 훈련은 후속 범위</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -5247,19 +5315,23 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr"/>
+          <t>기록·검증</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>주요 행동</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
+          <t>보고서는 독립된 대메뉴에서 새로 시작하는 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
@@ -5267,190 +5339,450 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>데이터 연계</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>원천·주기·권한·상태·스키마 관리</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>임계치·규칙</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>지점·유형별 기준, 변화율, 사건 연결 규칙</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>현재 사건 요약과 누락 정보 안내</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr"/>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>전파 대상</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>부서·기관·지역·매체·권한</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>유사 사건·과거 결정 탐색</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·입출력·유효시간·검증상태</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>전파문·상황보고서 초안 작성</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr"/>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>사용자·권한</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>역할, 승인권한, 개인정보 접근</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>후속 제품 범위</t>
-        </is>
-      </c>
+          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr"/>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
+          <t>원천에 없는 사실 생성 금지</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>확실성·한계를 숨긴 단정 금지</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>담당자 승인 대행 금지</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr"/>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr"/>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>데이터 연계</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>원천·주기·권한·상태·스키마 관리</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>위험도·알림 규칙</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>지점·유형별 임계치·변화율, 매트릭스 가중치·구간·결측 처리, 알림·사건 연결 규칙</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>전파 대상</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>부서·기관·지역·매체·권한</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>모델·버전·입출력·유효시간·검증상태</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>사용자·권한</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>역할, 승인권한, 개인정보 접근</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>후속 제품 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
           <t>관리 화면 수는 대표 데모 성과에 포함하지 않는다.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5708,7 +6040,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>/incidents</t>
+          <t>/scr-01</t>
         </is>
       </c>
     </row>
@@ -5740,7 +6072,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>/incidents → /incidents/:incidentId</t>
+          <t>/scr-01 → /scr-02/:districtId</t>
         </is>
       </c>
     </row>
@@ -5772,7 +6104,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
     </row>
@@ -5804,7 +6136,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
     </row>
@@ -5831,12 +6163,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>근거 목록의 예측 이벤트를 눌러 지도를 디지털트윈 화면으로</t>
+          <t>근거 목록의 예측 이벤트를 눌러 디지털트윈 화면으로</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/twin?forecastId=...</t>
+          <t>/scr-05/:districtId</t>
         </is>
       </c>
     </row>
@@ -5868,7 +6200,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/twin?forecastId=...&amp;alternativeId=...</t>
+          <t>/scr-05/:districtId</t>
         </is>
       </c>
     </row>
@@ -5895,12 +6227,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SOP·전파·시설 요청 승인</t>
+          <t>/scr-02 집중 팝업에서 SOP·전파·시설 요청 승인</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/response</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
     </row>
@@ -5927,12 +6259,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>실패·대체조치 기록</t>
+          <t>집중 팝업에서 실패·대체조치 기록</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>/incidents/:incidentId/response</t>
+          <t>/scr-02/:districtId</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6296,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>/records/:incidentId</t>
+          <t>/scr-04 → /scr-07?event=...</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6049,114 +6381,126 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>selectedForecastId</t>
+          <t>selectedAlertId</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>선택한 기준·대안 예측판 유지</t>
+          <t>IA-01에서 선택한 복합 알림과 후보 생성 근거 유지</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>affectedGeometryId</t>
+          <t>selectedForecastId</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>같은 영향범위와 대상 사용</t>
+          <t>선택한 기준·대안 예측판 유지</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>selectedEvidenceId</t>
+          <t>affectedGeometryId</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>IA-02·03에서 선택한 관측·영상·분석 근거를 트윈·대응에서도 유지</t>
+          <t>같은 영향범위와 대상 사용</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>pendingDecisionId</t>
+          <t>selectedEvidenceId</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>검토 중인 승인안 유지</t>
+          <t>IA-02·03에서 선택한 관측·영상·분석 근거를 트윈·대응에서도 유지</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ingestionMode</t>
+          <t>pendingDecisionId</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>혼합 데모에서도 이벤트별 실시간·재생·모의·수동 방식을 구분</t>
+          <t>검토 중인 승인안 유지</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>scenarioMode</t>
+          <t>ingestionMode</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>사건 현상·예측 데이터가 정렬된 과거 재생·혼합 데모·완전 모의 중 무엇인지 유지</t>
+          <t>혼합 데모에서도 이벤트별 실시간·재생·모의·수동 방식을 구분</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dataOrigin</t>
+          <t>scenarioMode</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>이벤트가 실제 API·원본 파일·승인 표본·합성 데이터·사용자 입력 중 어디서 왔는지 유지</t>
+          <t>사건 현상·예측 데이터가 정렬된 과거 재생·혼합 데모·완전 모의 중 무엇인지 유지</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>scenarioId</t>
+          <t>dataOrigin</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D8에서 생성한 훈련 시나리오와 원 사건 스냅샷 연결</t>
+          <t>이벤트가 실제 API·원본 파일·승인 표본·합성 데이터·사용자 입력 중 어디서 왔는지 유지</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>scenarioId</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D8에서 생성한 훈련 시나리오와 원 사건 스냅샷 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>trainingRunId</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>같은 시나리오의 개별 훈련 실행·결정·결과 구분</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>화면이 각자 사건 상태와 시간을 복제해서 소유하지 않는다.</t>
         </is>
@@ -6173,7 +6517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6218,109 +6562,109 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>AttentionAlert</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>전 공간</t>
+          <t>IA-01·02·05</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>사건 위험유형·트윈 유형군·범위·처리상태·위험판단·관계</t>
+          <t>단일/복합/예측/품질/공식 상황 유형, 등급·상태·대상·근거 이벤트·Forecast·연결 이유·규칙 버전·반복 억제</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IA-01·02·03·05</t>
+          <t>전 공간</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·기준시각·조건·결과·불확실성</t>
+          <t>사건 위험유형·트윈 유형군·범위·처리상태·매트릭스 위험등급·기여도와 4축 설명·관계</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AffectedArea</t>
+          <t>Forecast</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IA-01·02·03·04</t>
+          <t>IA-01·02·03·05</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>현재/예상 구분, 공간·대상·도달시간</t>
+          <t>모델·버전·기준시각·조건·결과·불확실성</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>AffectedArea</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-01·02·03·04</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>권고·제안 대응수준·근거·반대근거·생성주체</t>
+          <t>현재/예상 구분, 공간·대상·도달시간</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>IA-02·04·05</t>
+          <t>IA-04</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>검토중·선택·승인·기각·취소, 선택 대응수준·담당자·시각·사유</t>
+          <t>권고·제안 대응수준·근거·반대근거·생성주체</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IA-04·05</t>
+          <t>IA-02·04·05</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SOP·전파·시설 요청·담당·상태</t>
+          <t>검토중·선택·승인·기각·취소, 선택 대응수준·담당자·시각·사유</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -6330,31 +6674,31 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>사건 결과·현장·예측/대응 검증과 참조 근거</t>
+          <t>SOP·전파·시설 요청·담당·상태</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CityOperationalState</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>IA-01·02·05</t>
+          <t>IA-04·05</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>시 전체 대응단계·변경시각·승인 결정·관련 사건</t>
+          <t>사건 결과·현장·예측/대응 검증과 참조 근거</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ExternalRecord</t>
+          <t>CityOperationalState</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -6364,99 +6708,116 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>외부 특보·기관 사건의 원본 ID와 변경 이력</t>
+          <t>시 전체 대응단계·변경시각·승인 결정·관련 사건</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ReviewRequest</t>
+          <t>ExternalRecord</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IA-02·05</t>
+          <t>IA-01·02·05</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>확인 대상·요청 사유·담당·상태</t>
+          <t>외부 특보·기관 사건의 원본 ID와 변경 이력</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ModelRun</t>
+          <t>ReviewRequest</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>IA-03·05</t>
+          <t>IA-02·05</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>실행 요청 조건·미지원·미실행/실행중/완료/실패 상태와 생성 예측판</t>
+          <t>확인 대상·요청 사유·담당·상태</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>ModelRun</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IA-05</t>
+          <t>IA-03·05</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>초안·확정본·버전·생성 근거</t>
+          <t>실행 요청 조건·미지원·미실행/실행중/완료/실패 상태와 생성 예측판</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TrainingScenario</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>IA-05·IA-T01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>원 사건 스냅샷·이벤트·Forecast·대응 이력 참조, 훈련 조건·목표·버전</t>
+          <t>초안·확정본·버전·생성 근거</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>TrainingScenario</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>IA-05·IA-T01</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>원 사건 스냅샷·이벤트·Forecast·대응 이력 참조, 훈련 조건·목표·버전</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>TrainingRun</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>IA-T01</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>시나리오별 실행상태·참여자·훈련 결정·조치·결과·회고</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>같은 객체를 화면마다 다른 값으로 복제하지 않고, 질문에 맞는 요약만 다르게 보여준다.</t>
         </is>
@@ -6751,7 +7112,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IA-02</t>
+          <t>IA-02 지도 중심 사건 작업공간·좌측 관련 이벤트 현황</t>
         </is>
       </c>
     </row>
@@ -6853,7 +7214,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-02 판단·전망 요약과 IA-04 대응 집중 팝업</t>
         </is>
       </c>
     </row>

--- a/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
+++ b/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-14 11:55 생성). 값이 갈리면 md 가 이긴다</t>
+          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-15 15:24 생성). 값이 갈리면 md 가 이긴다</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D 산불·F 지반의 정적 개념 예시(R0)</t>
+          <t>D 산불·F 지반·G 정전의 개념 장면(R0·R1, 계산 아님)과 디지털트윈 메뉴의 인셋·보조뷰·선·노드·벡터·격자 부품</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C·D·F 비교는 IA-03 유형 전환으로 설계한다. C 모의 예측과 R0인 D·F 정적 개념 예시는 I4 선택 범위다.</t>
+          <t>유형은 디지털트윈 메뉴의 축이고 일곱 유형이 모두 선다(03 §5, 2026-09-15). D·F·G 는 개념 장면이며 표현 부품(인셋·보조뷰·선·노드·벡터·격자)은 I4 선택 범위다.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련은 사이드바 메뉴(IA-T01)로 설계한다. D8 진입점은 포함하고, 일정이 허용하면 A 시나리오 목록과 실행을 선택 에필로그로 만든다. 편집·예약과 C 유형 훈련은 후속 범위다. 실행 화면은 Phase 1 트윈 페이지를 사전 조건분석으로 쓰며 IA-05의 대응 이력이 시나리오의 입력이 된다.</t>
+          <t>사이드바 메뉴는 디지털트윈이다(2026-09-15 결정). 사건 없이 유형·지역·조건 세트로 트윈을 열고, 훈련(IA-T01)은 그 안의 행동(훈련 시작 → 결정 기록 → 종료)이다. D8 진입점은 종료 사건의 스냅샷을 만들어 같은 메뉴로 보낸다. 편집·예약과 C 유형 훈련은 후속 범위다. 유형별 장면·광역 인셋은 03_유형별디지털트윈.md 제2부가 소유한다.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>선택 에필로그를 구현할 경우 D8 원 사건에서 IA-T01 훈련 시나리오를 생성할 입력·참조 ID 계약을 구현 설계에서 확정한다.</t>
+          <t>훈련 중 조건이 바뀌면 새 회차로 칠지, 그리고 B 유형의 메뉴 포함·G 유형의 자리(독립 대 A 파생)·E 격자 노출 장면 제작을 사용자 결정으로 확정한다.</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>/scr-05/:districtId</t>
+          <t>/scr-02/:districtId?panel=twin</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>승인·실행 결과를 추적하고 대응중·통제로 전환</t>
+          <t>승인·실행 결과를 추적하고 통제 국면으로 전환</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>통제·종료 사건 또는 과거 사건 조회</t>
+          <t>통제 국면·종료 사건 또는 과거 사건 조회</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>사이드바 메뉴·독립 훈련 흐름</t>
+          <t>사이드바 디지털트윈 메뉴 안의 행동</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1962,23 +1962,23 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>훈련 진입점, 선택 시 A 시나리오 목록·실행·이력</t>
+          <t>조건 세트·지역·사건 스냅샷, 훈련 기록</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>선택 에필로그</t>
+          <t>D8 진입점 필수 · 실행은 구현됨</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D8 진입점 또는 선택 에필로그의 A 훈련 시나리오 선택</t>
+          <t>디지털트윈 메뉴에서 유형·지역·조건 선택, 또는 D8 스냅샷</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈 화면(사전 조건분석)에서 대응 연습, 훈련 이력 기록</t>
+          <t>같은 트윈에서 대안·시각을 고르고 결정을 기록, 훈련 이력</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·확인됨·대응중·통제 사건, 매트릭스 위험등급, 긴급도, 확실성, 경과시간</t>
+          <t>후보·확인중·대응중 사건(통제 국면 표시), 매트릭스 위험등급, 긴급도, 확실성, 경과시간</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·확인됨·대응중·통제·종료·오탐·병합됨</t>
+          <t>후보·확인중·대응중·종료·오탐·병합됨. 대응중 안의 국면 통제</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -4875,7 +4875,7 @@
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>사건을 대응중 또는 통제로 전환</t>
+          <t>사건을 통제 국면으로 전환</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>정적 개념 예시. 대표 사례 산불</t>
+          <t>개념 장면(시간·대안 동작, 계산 아님). 대표 사례 산불</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>정적 개념 예시</t>
+          <t>개념 장면(시간·대안 동작, 계산 아님)</t>
         </is>
       </c>
     </row>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>근거 목록의 예측 이벤트를 눌러 디지털트윈 화면으로</t>
+          <t>근거 목록의 예측 이벤트를 눌러 같은 지도가 예측 모드로</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>/scr-05/:districtId</t>
+          <t>/scr-02/:districtId?panel=twin</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>/scr-05/:districtId</t>
+          <t>/scr-02/:districtId?panel=twin</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IA-03 디지털트윈(사건 지도 안) · IA-T01 훈련 실행 화면</t>
+          <t>IA-03 디지털트윈(사건 지도 안) · /scr-05 디지털트윈 메뉴</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>IA-T01 대응 모의훈련의 실행 화면. 이름은 사전 조건분석</t>
+          <t>디지털트윈 메뉴의 조건 세트(유형·지역·조건 → 사전 작성 예측판). 상승률 계산은 폐기</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>유지</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>03_유형별디지털트윈.md의 E 대기·면 노출 장기 후보</t>
+          <t>E 대기·면 노출의 개념 예시. 03 §23 광역 인셋 재료 (2026-09-15, 앞선 "제외" 대체)</t>
         </is>
       </c>
     </row>

--- a/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
+++ b/docs/고도화/CUVIA_NDMS_기능및정보구조도.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-15 15:24 생성). 값이 갈리면 md 가 이긴다</t>
+          <t>CUVIA_NDMS_기능및정보구조도.md · 이 엑셀은 md 를 표로 옮긴 동기화본 (2026-09-16 17:44 생성). 값이 갈리면 md 가 이긴다</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IA 기준안 - 재검수 잔여항목 반영·엑셀 동기화 완료</t>
+          <t>IA 기준안 - 재검수 잔여항목 반영·엑셀 동기화 완료. 2026-09-16 `/scr-05` 를 모의훈련(IA-07 · 옛 IA-03M)으로 고치고 전망 탭 대안 비교를 되살림(README §2.3)</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>화면 넷과 디지털트윈이 각각 하나의 핵심 질문에 답하고, 대응 모의훈련은 D8 진입점에서 후속 확장된다.</t>
+          <t>화면 넷과 모의훈련이 각각 하나의 핵심 질문에 답하고, 사건이 끝나면 예측 케이스가 IA-05 에 쌓인다. 개선 항목은 검증·훈련이 한 목록으로 쓴다.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>사건 우선 큐에서 대표 후보 진입</t>
+          <t>실시간 주요 사건에서 대표 후보 진입</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>예측 이벤트를 누르면 사건 지도가 디지털트윈 화면으로 바뀌는 흐름과 대안 선택</t>
+          <t>예측 이벤트를 누르면 사건 지도가 디지털트윈 화면으로 바뀌는 흐름과, 같은 전망 탭에서 대응을 바꿔 보는 비교</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D8의 대응 모의훈련 진입점. A 시나리오 목록·실행은 일정이 허용할 때 선택 에필로그로 구현하고 편집·예약과 C 훈련은 제외</t>
+          <t>D8의 예측 케이스 확정과 예측 대 실제 비교(IA-05 이력 · 사건 기록 창의 ⑤ 예측 검증 절)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>A 대응 모의훈련 목록·실행 에필로그. 편집·예약과 C 유형 훈련은 후속 범위</t>
+          <t>모의훈련(IA-07): 지난 사건 시나리오 · 비교 · 개선 항목. 어느 사건을 넣을지는 README §7. 인셋·보조뷰·선·노드·벡터·격자 부품</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C 해안 월류의 시나리오 Forecast 기반 모의 예측 화면(R1)</t>
+          <t>G 펌프 장애가 독립 고장 기준을 넘을 때 별도 사건으로 분리되는 관계 표시</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D 산불·F 지반·G 정전의 개념 장면(R0·R1, 계산 아님)과 디지털트윈 메뉴의 인셋·보조뷰·선·노드·벡터·격자 부품</t>
+          <t>사건 AI 보조 오버레이와 운영 관리 보조 구조</t>
         </is>
       </c>
     </row>
@@ -1180,31 +1180,31 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>G 펌프 장애가 독립 고장 기준을 넘을 때 별도 사건으로 분리되는 관계 표시</t>
+          <t>C 모의 예측과 G 파생 장면은 제품 방향에는 포함하되 대표 도시침수 D0~D8의 완료 조건에는 넣지 않는다. 항목별 일정과 시연 효과를 확인해 I4에서 선택한다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>기록·검증 정리, 사건 AI 보조 오버레이와 운영 관리 보조 구조</t>
+          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 일정이 허용할 때 선택 확장</t>
+          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C 모의 예측과 G 파생 장면은 제품 방향에는 포함하되 대표 도시침수 D0~D8의 완료 조건에는 넣지 않는다. 항목별 일정과 시연 효과를 확인해 I4에서 선택한다.</t>
+          <t>기준·대안 예측판 비교</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CCTV/VLM 결과와 실제 영상 교차확인</t>
+          <t>영향 대상과 실제 SOP·전파문 연결</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>기준·대안 예측판 비교</t>
+          <t>예측과 실제 관측의 오차 검증</t>
         </is>
       </c>
     </row>
@@ -1240,31 +1240,31 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>영향 대상과 실제 SOP·전파문 연결</t>
+          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 디지털트윈 화면은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하며 기본 제품 UI에 제작 설명을 노출하지 않는다. 검증되지 않은 모델 성능이나 실제 운영 성과로 대외 주장하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>예측과 실제 관측의 오차 검증</t>
+          <t>모든 유형의 동적 모델</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 데이터 확보 시 강화</t>
+          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>정렬된 과거 자료와 실제 모델 결과가 없으면 A 유형은 R1을 유지한다. 디지털트윈 화면은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하며 기본 제품 UI에 제작 설명을 노출하지 않는다. 검증되지 않은 모델 성능이나 실제 운영 성과로 대외 주장하지 않는다.</t>
+          <t>실제 재난문자·시설 원격제어</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>모든 유형의 동적 모델</t>
+          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>실제 재난문자·시설 원격제어</t>
+          <t>예측 케이스의 유사 사건 추천·SOP 임계값 개선·모델 보정(향후 활용)</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>임계치·SOP·사용자·권한 관리 전체 화면</t>
+          <t>대규모 운영 통계와 SLA</t>
         </is>
       </c>
     </row>
@@ -1312,31 +1312,31 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련 시나리오 편집·예약과 C 유형 훈련. A 목록·실행은 선택 에필로그 IA-T01</t>
+          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>대규모 운영 통계와 SLA</t>
+          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>§18 Phase 2 데모 범위 · 대표 데모 밖</t>
+          <t>§19 화면 정의 완료 조건</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>R0 유형을 실제 계산하는 것처럼 보이는 화면</t>
+          <t>답할 사용자 질문</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>각 화면 또는 작업영역은 다음 항목을 가져야 구현 대상으로 확정할 수 있다.</t>
+          <t>사용하는 공통 객체와 필드</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>답할 사용자 질문</t>
+          <t>진입 조건과 다음 행동</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>사용하는 공통 객체와 필드</t>
+          <t>시스템 생성 정보와 담당자 결정의 구분</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>진입 조건과 다음 행동</t>
+          <t>정상·빈·지연·결측·실패 상태와 내부 시나리오 처리</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>시스템 생성 정보와 담당자 결정의 구분</t>
+          <t>데이터·모델·업무 근거와 준비도</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>정상·빈·지연·결측·실패 상태와 내부 시나리오 처리</t>
+          <t>대표 데모 포함 여부</t>
         </is>
       </c>
     </row>
@@ -1420,31 +1420,31 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>데이터·모델·업무 근거와 준비도</t>
+          <t>기존 자산의 재사용·재편·제외 판정</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>대표 데모 포함 여부</t>
+          <t>다음은 현재 기준안에서 결정됐다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>§19 화면 정의 완료 조건</t>
+          <t>§20 결정된 화면 기준과 남은 확인</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>기존 자산의 재사용·재편·제외 판정</t>
+          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 실시간 주요 사건에 나타나면 IA-02로 연다.</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>다음은 현재 기준안에서 결정됐다.</t>
+          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D0는 IA-01의 감시 우선대상에서 시작하고, D1에 생성된 후보가 사건 우선 큐에 나타나면 IA-02로 연다.</t>
+          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다. 이력의 [보고서] 탭이 사건 보고서를 모으고, 분석 보고서는 모의훈련이 소유한다(2026-09-16).</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>AI 보조는 공통 근거 탐색·요약으로 두며 독립 판단 사일로로 만들지 않는다.</t>
+          <t>이력(IA-05)과 통계(IA-06)는 별도 메뉴다(2026-09-16). 예측 검증은 사건 한 건의 기록이라 통계에 두지 않고 이력의 사건 기록 창에 이벤트 이력과 함께 둔다. 종합상황·모의훈련·이력·통계의 사건 목록은 같은 사건 원장에서 나오고 사건 수·상태가 같다.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>보고서는 IA-05에서 사건 기록으로 생성하는 산출물로 둔다.</t>
+          <t>P0 자료 확인 전 IA-03은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하고, 기본 제품 UI에 제작 설명을 넣지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>P0 자료 확인 전 IA-03은 사전 작성한 시나리오 Forecast로 목표 제품의 흐름을 보여준다. 데이터 구성과 실제 모델 교체 대상은 내부 계약에서 관리하고, 기본 제품 UI에 제작 설명을 넣지 않는다.</t>
+          <t>IA-02는 Phase 1 지구 재난관제와 좌우 패널 골조를 지도 중심 사건 작업공간으로 재편한다. 좌측은 선택한 알림·사건의 관련 이벤트 현황, 우측은 판단·전망과 대응 결과 요약이며 사건 범위는 지점부터 도시 전역까지 수용한다.</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>IA-02는 Phase 1 지구 재난관제와 좌우 패널 골조를 지도 중심 사건 작업공간으로 재편한다. 좌측은 선택한 알림·사건의 관련 이벤트 현황, 우측은 판단·전망과 대응 결과 요약이며 사건 범위는 지점부터 도시 전역까지 수용한다.</t>
+          <t>IA-03 디지털트윈은 독립 페이지가 아니라 사건 작업공간 안에서 예측 이벤트를 눌러 여는 디지털트윈 화면이다. IA-04 대응 승인·실행은 사건 위의 집중 팝업으로 분리한다. 화면 배치와 전환은 04 정본을 따른다.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>IA-03 디지털트윈은 독립 페이지가 아니라 사건 작업공간 안에서 예측 이벤트를 눌러 여는 디지털트윈 화면이다. IA-04 대응 승인·실행은 사건 위의 집중 팝업으로 분리한다. 화면 배치와 전환은 04 정본을 따른다.</t>
+          <t>IA-05 이력은 상시 메뉴로 두되 대표 데모의 주 동선에서는 D8 사건 종료가 그 사건의 기록 창으로 들어온다.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>IA-05는 상시 접근 가능한 독립 페이지로 두되 대표 데모의 주 동선에서는 D8에 진입한다.</t>
+          <t>디지털트윈의 축은 사건이다(2026-09-16). 유형별 장면은 사건이 가리키는 유형을 따른다. A 는 진행 중 대표 사건(전망 탭), B~G 는 모의훈련의 지난 사건이며(03 §16) 어느 사건을 Phase 2에 보일지는 README §6.1에서 정한다. 표현 부품은 I4 선택 범위다.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>유형은 디지털트윈 메뉴의 축이고 일곱 유형이 모두 선다(03 §5, 2026-09-15). D·F·G 는 개념 장면이며 표현 부품(인셋·보조뷰·선·노드·벡터·격자)은 I4 선택 범위다.</t>
+          <t>G 파생 관계 표시도 I4 선택 범위다. 대표 데모 필수 범위는 도시침수 D0~D8과 D8의 예측 케이스 확정까지다.</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>G 파생 관계 표시도 I4 선택 범위다. 대표 데모 필수 범위는 도시침수 D0~D8과 D8의 TrainingScenario 생성 진입점·전달 계약까지다.</t>
+          <t>사이드바 /scr-05 메뉴는 모의훈련(IA-07)이다(2026-09-16 · README §2.3. 같은 날 앞선 "디지털트윈 = 사건 기반 대응 What-if"와 09-15 "모의훈련 모드 폐기"를 고친다). 진행 중 사건의 "지금 대응하면?"은 IA-03 전망 탭이 맡고, 모의훈련은 지난 사건에서 "이런 상황에서 이렇게 대응했다면?"을 본다. 바꾸는 것은 상황(조건 단계·유형 결합)과 대응(유형·조정값)이고 조합마다 사전 작성 판을 쓴다. 수치는 README §2.3 기준 ③을 넘는 것만 선다. 예측 대 실제 비교는 IA-05 예측 케이스(§13.1)다. 유형별 장면·광역 인셋은 03_유형별디지털트윈.md 제2부가 소유한다. 차별점 기준은 README §2.2 다.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>사이드바 메뉴는 디지털트윈이다(2026-09-15 결정). 사건 없이 유형·지역·조건 세트로 트윈을 열고, 훈련(IA-T01)은 그 안의 행동(훈련 시작 → 결정 기록 → 종료)이다. D8 진입점은 종료 사건의 스냅샷을 만들어 같은 메뉴로 보낸다. 편집·예약과 C 유형 훈련은 후속 범위다. 유형별 장면·광역 인셋은 03_유형별디지털트윈.md 제2부가 소유한다.</t>
+          <t>남은 확인은 다음 두 가지다.</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>남은 확인은 다음 두 가지다.</t>
+          <t>모의훈련에서 Phase 2에 보일 사건·유형과 비전 항목의 범위를 README §6.1에서 정한다(B·G·E 자리는 2026-09-16 지난 사건으로 닫혔다).</t>
         </is>
       </c>
     </row>
@@ -1600,19 +1600,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>훈련 중 조건이 바뀌면 새 회차로 칠지, 그리고 B 유형의 메뉴 포함·G 유형의 자리(독립 대 A 파생)·E 격자 노출 장면 제작을 사용자 결정으로 확정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>§20 결정된 화면 기준과 남은 확인</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>실제 기관의 메뉴 권한과 운영 절차를 확인해 IA-05 상시 접근 권한과 훈련 관리 책임 조직을 정한다. 이번 데모에서는 확정하지 않고 추후 제품 개발 시 정의한다.</t>
+          <t>실제 기관의 메뉴 권한과 운영 절차를 확인해 IA-05 상시 접근 권한과 예측 케이스 관리 책임 조직을 정한다. 이번 데모에서는 확정하지 않고 추후 제품 개발 시 정의한다.</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1813,17 +1801,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>그대로 두면 어떻게 되고 대안은 무엇인가?</t>
+          <t>그대로 두면, 지금·더 빨리 대응하면 언제·어디가·얼마나 위험해지는가?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>기준·대안 예측판과 영향</t>
+          <t>기준·대안 예측판과 영향 대상 · [이 전망으로 조치안 갱신]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>D4~D5 핵심</t>
+          <t>D4·D5 핵심</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1834,7 +1822,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>시각·대안을 고르고 [이 전망으로 대응 검토]로 대응 검토 시작</t>
+          <t>시각을 고르고 기준·대안을 견준 뒤 [이 전망으로 조치안 갱신]으로 대응 검토 시작</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1870,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>승인·실행 결과를 추적하고 통제 국면으로 전환</t>
+          <t>승인·실행 결과를 추적하고 안정 국면으로 전환</t>
         </is>
       </c>
     </row>
@@ -1894,27 +1882,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>상시 메뉴·독립 화면</t>
+          <t>상시 메뉴 이력 · 탭 [사건 · 보고서]</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>/scr-04, /scr-07?event=...</t>
+          <t>/scr-07</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>무엇을 예측·결정했고 실제 결과는 어땠는가?</t>
+          <t>이 사건은 어떻게 흘러갔고, 예측은 맞았는가?</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>사건 기록·검증·보고서</t>
+          <t>사건 기록(이벤트 이력·예측 검증)·사건 보고서</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,137 +1913,145 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>통제 국면·종료 사건 또는 과거 사건 조회</t>
+          <t>D8 사건 종료, 종료·오탐·병합 사건 안내, 과거 사건 조회</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>검증·보고서·개선 항목 확정, 필요하면 사건 재개</t>
+          <t>사건 기록에서 경과와 예측 검증 확인, 보고서 확정·보고</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IA-T01</t>
+          <t>IA-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>대응 모의훈련</t>
+          <t>통계</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>사이드바 디지털트윈 메뉴 안의 행동</t>
+          <t>상시 메뉴 통계</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>/scr-05</t>
+          <t>/scr-04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>이 조건이면 어떻게 대응할 것인가?</t>
+          <t>기간 동안 어떤 사건이 어디서 얼마나 났고, 대응은 어땠는가?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>조건 세트·지역·사건 스냅샷, 훈련 기록</t>
+          <t>사건·대응 집계</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>D8 진입점 필수 · 실행은 구현됨</t>
+          <t>상시 조회 · 데모 주동선 밖</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈 메뉴에서 유형·지역·조건 선택, 또는 D8 스냅샷</t>
+          <t>기간·지역·유형별 발생과 대응을 모아 볼 때</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>같은 트윈에서 대안·시각을 고르고 결정을 기록, 훈련 이력</t>
+          <t>많이 난 곳·유형을 찾고, 한 사건의 경과는 이력에서 연다</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>AI 보조</t>
+          <t>모의훈련</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>현재 화면 위 공통 보조</t>
+          <t>사이드바 모의훈련 메뉴</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>/scr-06</t>
+          <t>/scr-05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>현재 사건의 근거를 어떻게 빨리 찾는가?</t>
+          <t>이런 상황에서 이렇게 대응했다면 어땠을까?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>근거 요약·해당 위치 이동</t>
+          <t>시나리오(상황·대응·유형 결합)·비교·상황 부여·분석 결과·개선 항목</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>지난 사건 · Phase 2 범위는 README §7 (2026-09-16, 옛 IA-03M)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>사이드바 모의훈련에서 지난 사건 선택, 또는 저장된 분석 다시 열기</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>분석 기준 시점 → 시나리오(상황·대응·유형 결합) → 비교 → 개선 항목. 바닥 동작은 [분석 결과 저장]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
+          <t>AI 보조</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>관리자 메뉴</t>
+          <t>현재 화면 위 공통 보조</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>추후 정의</t>
+          <t>/scr-06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>기준·SOP·연계 대상을 어떻게 관리하는가?</t>
+          <t>현재 사건의 근거를 어떻게 빨리 찾는가?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>운영 설정</t>
+          <t>근거 요약·해당 위치 이동</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>데모 밖</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -2063,20 +2059,60 @@
       <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>관리자 메뉴</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>추후 정의</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>IA ID는 설계상 식별자이며 기존 SCR 번호나 최종 URL을 뜻하지 않는다.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>기준·SOP·연계 대상을 어떻게 관리하는가?</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>운영 설정</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>데모 밖</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>IA ID는 설계상 식별자이며 기존 SCR 번호나 최종 URL을 뜻하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2089,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2238,12 +2274,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>사건 우선 큐</t>
+          <t>실시간 주요 사건</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·대응중 사건(통제 국면 표시), 매트릭스 위험등급, 긴급도, 확실성, 경과시간</t>
+          <t>후보·확인중·대응중 사건(안정 국면 표시), 매트릭스 위험등급, 긴급도, 확실성, 경과시간</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2423,7 +2459,7 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>담당자·상태·유형으로 우선 큐 필터링</t>
+          <t>담당자·상태·유형으로 실시간 주요 사건 거르기</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -2755,7 +2791,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>후보·확인중·대응중·종료·오탐·병합됨. 대응중 안의 국면 통제</t>
+          <t>후보·확인중·대응중·종료·오탐·병합됨. 대응중 안의 국면 안정</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -3763,7 +3799,7 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>사건 작업공간 안의 디지털트윈 화면이다. 담당자가 근거 목록이나 타임라인의 예측 이벤트를 누르면 같은 지도가 그 시각의 3D 디지털트윈 화면으로 바뀐다. 독립 페이지가 아니다. 현재 상태와 미래 전망을 구분하고, 조건을 바꿨을 때 영향이 어떻게 달라지는지 비교한다. 대응 모의훈련(IA-T01)이 같은 디지털트윈 화면을 사건 없이 사용한다.</t>
+          <t>사건 작업공간 안의 디지털트윈 화면이다. 담당자가 근거 목록이나 타임라인의 예측 이벤트를 누르면 같은 지도가 그 시각의 3D 디지털트윈 화면으로 바뀐다. 독립 페이지가 아니다. 현재 상태와 미래 전망을 구분하고 기준 전망("그대로면?")과 대안 비교("지금·더 빨리 대응하면?")를 한 탭에서 보여 준다. 진행 중 사건의 대응 판단은 이 탭이 끝까지 들고 모의훈련으로 넘기지 않는다 (2026-09-16 · README §2.3. 같은 날 앞선 "[디지털트윈에서 비교]로 넘긴다"를 고친다). 두 전망은 같은 트윈의 결과다.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3850,17 +3886,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>대안 선택</t>
+          <t>그대로 두면</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>그대로 / 도로 통제 / 배수 대응</t>
+          <t>최대값·도달 예상·영향 대상(도로·중요시설·건물·이용자)과 상태·시각·요약 한 줄. 대상 수는 자료 경로가 확인된 뒤에 붙인다(2026-09-16)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>신설</t>
+          <t>영향 결과 카드를 기준 한 열로</t>
         </is>
       </c>
     </row>
@@ -3882,17 +3918,17 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>영향 결과</t>
+          <t>대안 비교</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>기준 전망과 대안 전망의 2열 비교</t>
+          <t>대응 유형·시작 시점 선택지와 기준 대비 달라지는 지표. 수치는 README §2.3 기준 ③(경로·트윈 결과)을 넘는 것만. 노출 대응은 도달 전 여유 시간</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>영향 결과 카드. 열 제목만 바뀜</t>
+          <t>2026-09-15 전망 탭 대안 비교표(README §8.2)</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4359,7 @@
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>대안 선택(그대로 / 도로 통제 / 배수 대응)으로 기준 대 대안 비교</t>
+          <t>대안 비교: 대응 유형·시작 시점을 골라 기준과 견준다. 대안 예측판이 없는 사건은 닫히고 이유가 한 줄로 선다</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4371,7 +4407,7 @@
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>[이 전망으로 대응 검토]: 선택한 시각·대안을 가지고 대응 집중 팝업을 연다. 권고 카드에 전망 기준이 표시된다</t>
+          <t>[이 전망으로 조치안 갱신]: 선택한 시각의 기준 전망으로 대응 집중 팝업을 연다. 권고 카드에 전망 기준이 표시된다</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4419,7 +4455,7 @@
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
+          <t>R0 유형은 계산 결과를 주장하지 않는다. 2026-09-16 C~G 를 지난 사건으로 세웠고(03 §5·§16) 모의훈련(IA-07)에서 연다. 값은 사전 작성 예측판이다. 수치는 03 §15 경로 표와 README §2.3 기준 ③을 따르고, 어느 사건을 Phase 2에 보일지는 README §6.1에서 정한다. 실시간 물리 계산처럼 부르지 않고, 모델이 연결되면 같은 계약의 ModelRun 결과로 교체한다.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4443,7 +4479,7 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
+          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 국면 안정과 도로·시설 통제 Action은 서로 다른 값이다. 국면의 옛 이름 통제가 Action 과 같은 이름이라 2026-09-16 안정으로 바꿨다.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4491,7 +4527,7 @@
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>지원하지 않는 대안은 대안 선택에 나타나지 않는다. 미지원·미실행·실패는 ModelRun 상태값으로만 기록하고 화면 라벨로 두지 않는다.</t>
+          <t>지원하지 않는 대안은 트윈의 대응 선택에 나타나지 않는다. 미지원·미실행·실패는 ModelRun 상태값으로만 기록하고 화면 라벨로 두지 않는다.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4875,7 +4911,7 @@
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>사건을 통제 국면으로 전환</t>
+          <t>사건을 안정 국면(상황 안정)으로 전환</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -4984,18 +5020,14 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>사건 진행과 판단 근거를 재구성하고 예측·대응의 실제 결과를 검토한다.</t>
+          <t>두 메뉴는 같은 사건 원장을 본다. 이력은 사건 한 건을 되짚고, 통계는 여러 사건을 모아 센다. 같은 기간·조건이면 두 화면의 사건 수와 상태가 같다(2026-09-16). 종합상황의 실시간 주요 사건, 모의훈련의 지난 사건 목록도 같은 원장에서 나온다. 목적이 달라 칸은 달라도 사건 수·상태·시각은 갈리지 않는다.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -5008,22 +5040,14 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>사건 타임라인</t>
-        </is>
-      </c>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>원천 이벤트, 사건 상태, 예측판, 결정, 실행과 현장 결과</t>
+          <t>모의훈련의 분석 결과와 분석 보고서는 이력에 쌓지 않는다(2026-09-16). 이력은 "예측 대 실제"를 견주고, 모의훈련은 "실제(재현) 대 바꾼 조건"을 견준다. 분석 결과의 저장·조회·다시 열기·보고서는 모의훈련(IA-07)이 소유한다(03 §26). 개선 항목만은 한 목록이다. 예측 검증과 모의훈련이 찾은 고칠 거리를 출처(검증 · 훈련)만 달리해 모으고, 승인 뒤 반영한다(README §2.3).</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -5036,22 +5060,14 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>주요 시간</t>
-        </is>
-      </c>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>최초 감지·후보 생성·확인·전파·조치·통제·종료</t>
+          <t>진행 중 사건의 판단·승인·조작은 이력에서 하지 않는다. 그 일은 사건 작업공간(IA-02·04)이 한다. 이력은 읽는 자리다.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -5064,22 +5080,18 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>예측 검증</t>
-        </is>
-      </c>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>예측 대 실제, 과대·과소, 비교 불가 사유</t>
+          <t>메뉴 이름은 이력이고 상단 탭은 [사건] · [보고서] 둘이다. 모의훈련의 [지난 사건] · [저장된 분석]과 같은 문법으로, 일어난 일(사건)과 만들어진 문서(보고서)를 가른다. 두 게시판 모두 줄을 누르면 목록 위에 창이 뜬다.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -5092,25 +5104,29 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>10.1 IA-05 이력</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>대응 검토</t>
+          <t>[사건] 게시판</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>대기·진행중·성공·실패·미응답·확인대기·대체됨·취소와 소요시간</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
+          <t>되짚을 사건을 찾는다</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>사건명·범위 → 유형 → 상태(진행 중·종료·오탐·병합) → 발생·종료 시각 → 예측 검증·보고서가 있는지</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5120,25 +5136,29 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>10.1 IA-05 이력</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>보고서</t>
+          <t>사건 기록 창</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 초안, 근거 링크, 담당자 수정·확정</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
+          <t>이 사건이 무엇이었고, 왜 사건이 됐고, 무엇을 했고, 예측은 맞았는지 한 번에 안다</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>아래 여섯 절을 순서대로</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5148,25 +5168,29 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>내부 구성</t>
+          <t>10.1 IA-05 이력</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>개선 항목</t>
+          <t>[보고서] 게시판</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>임계치·모델·데이터·SOP 검토 과제</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
+          <t>확정·제출할 문서를 찾는다</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>보고서명 → 사건 → 상태(초안·확정본)·판 → 생성 시각</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5176,18 +5200,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>사건 종료 또는 재개</t>
+          <t>사건 기록 창은 탭으로 나누지 않고 한 번에 읽히는 기록이다(SK2 이벤트 상세 · SK 결과보고서와 같은 결). 경과 타임라인 하나로는 "이 사건이 무엇이었고 무엇을 했는지"가 보이지 않는다(2026-09-16 사용자 "이력이 너무 부실하다").</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -5200,21 +5228,29 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ① 사건 요약</t>
+        </is>
+      </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>예측판과 실제 관측 비교</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
+          <t>무엇이었나</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>사건 번호 · 유형 · 범위 · 최초 징후 · 사건 생성 · 종료 · 최고 위험 등급 · 담당·승인 · 연관 사건, 결과 한 줄</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5224,21 +5260,29 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ② 발생 근거</t>
+        </is>
+      </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>누락 근거·결과 보완 요청</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>왜 사건이 되었나</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>사건을 만든 알림과 연결 이유 → 근거 관측(수위·강우·조위·특보·영상·시설) → 예측판(기준시각·모델·도달 시각·최대값·영향 대상)과 그 예측의 실제 결과</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5248,21 +5292,29 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ③ 위험 판단</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>상황보고서 생성·수정·확정·내보내기</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
+          <t>어떻게 판단했나</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>위험 등급의 흐름(시각 · 등급 · 한 줄), 가장 높았던 판단의 요약</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5272,21 +5324,29 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ④ 대응</t>
+        </is>
+      </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>후속 개선 항목 등록</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr"/>
+          <t>무엇을 했나</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>결정·승인(누가 · 언제 · 무엇을 · 왜) → 조치(무엇 · 대상 · 담당 · 결과) → 전파(채널 · 결과 · 대체)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5296,21 +5356,29 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ⑤ 예측 검증 · 학습</t>
+        </is>
+      </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>이 사건의 대응 이력으로 대응 모의훈련 시나리오 후보 생성 요청. 목록·실행은 선택 에필로그 IA-T01, 편집·예약과 C 유형 훈련은 후속 범위</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr"/>
+          <t>근거가 된 예측은 맞았나, 다음에 무엇을 반영하나</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>§13.1의 넷: 무엇으로 예측했나 → 얼마나 맞았나 → 실제로 무엇을 했나 → 무엇을 고칠까(개선 항목 · 출처 검증·훈련)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5320,42 +5388,54 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>기록·검증</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>주요 행동</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16) · ⑥ 경과</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>보고서는 독립된 대메뉴에서 새로 시작하는 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다.</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr"/>
+          <t>전부 어떤 순서였나</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>시간순 타임라인(아래)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
+          <t>예측판은 사건을 일으킨 근거의 하나다. 그래서 예측은 ② 발생 근거 안에 관측과 나란히 서고, 그 카드에 실제 결과와 오차를 바로 붙인다. ⑤ 예측 검증은 그 근거가 실제와 얼마나 맞았는지 되짚고 다음 예측·임계치·SOP에 가져갈 것을 남기는 자리다. 오차는 실패가 아니라 학습 재료다(2026-09-16 사용자). 점수·등급은 매기지 않고, 모델 보정·재학습 자동화는 여전히 향후 활용이다(§13.1). 원장이 없는 지난 사건은 아는 것만 선다 — 발생 근거는 당시 상태 값과 예측판, 대응은 실제 대응 목록. 없는 절은 비었다고 말한다.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
@@ -5363,23 +5443,27 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>현재 사건 요약과 누락 정보 안내</t>
+          <t>⑥ 경과는 타임라인이다(CSMS 통합 타임라인 문법 · KISA 이력 탭과 같은 레일). 한 시간축에 두 갈래를 싣는다.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
@@ -5387,23 +5471,27 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+          <t>사건 흐름 — 무슨 일이 있었나. 관측·알림·위험 판단·예측판. 둥근 점이고 위험 단계 색을 쓴다.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -5411,23 +5499,27 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>유사 사건·과거 결정 탐색</t>
+          <t>조치 — 무엇을 했나. 확인·결정·승인·조치·전파·결과. 네모 점이고 종류는 짧은 뱃지로 적는다. 실패와 대체조치는 따로 보이게 한다.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
@@ -5435,23 +5527,27 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>전파문·상황보고서 초안 작성</t>
+          <t>종료 — 체크 아이콘으로 끝을 닫는다. 오탐·병합도 같은 자리에서 닫는다.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
@@ -5459,23 +5555,27 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>허용 역할</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+          <t>수집 이벤트를 전부 늘어놓지 않는다. 사건을 만들었거나 판단·조치가 참조한 이벤트만 선다. 원장에 없는 시각은 지어내지 않는다.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -5483,23 +5583,27 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>원천에 없는 사실 생성 금지</t>
+          <t>사건 기록 창의 바닥에는 [보고서]가 있으면 그 사건 보고서로 넘어가는 동작, 진행 중이면 [사건 작업공간] 동작이 선다. 창은 한 번에 하나다.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -5507,23 +5611,27 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>확실성·한계를 숨긴 단정 금지</t>
+          <t>두지 않는 것: 점수·등급·순위, 사건 편집, 이벤트 원장 전체 목록, 대안 분석 결과와 분석 보고서.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
@@ -5531,23 +5639,27 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
+          <t>10.1 IA-05 이력</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>사건 기록 창 — 읽는 순서 (2026-09-16)</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>담당자 승인 대행 금지</t>
+          <t>보고서는 독립된 업무가 아니라 사건 기록을 바탕으로 생성되는 결과물이다. [보고서] 탭은 그 결과물을 사건을 가로질러 찾는 자리다.</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -5555,23 +5667,23 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>IA-G01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>공통 AI 보조</t>
+          <t>이력 · IA-06 통계</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>제한</t>
+          <t>10.2 IA-06 통계</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+          <t>탭 없이 한 화면이다. 사건 한 건의 경과는 보지 않는다. 그것은 이력이 한다.</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
@@ -5579,210 +5691,602 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr"/>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>10.2 IA-06 통계</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>조회 조건</t>
+        </is>
+      </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr"/>
+          <t>볼 범위를 정한다</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>기간(기본 전체) · 지역 · 유형 · 상태</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr"/>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>10.2 IA-06 통계</t>
+        </is>
+      </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>데이터 연계</t>
+          <t>핵심 지표</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>원천·주기·권한·상태·스키마 관리</t>
+          <t>기간 전체를 한 줄로 안다</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>구조만 정의</t>
+          <t>사건 수(진행 중·종료·오탐·병합) → 발생에서 첫 대응까지 → 발생에서 종료까지 → 가장 많이 난 유형·지역</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr"/>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>10.2 IA-06 통계</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>위험도·알림 규칙</t>
+          <t>추이·분포</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>지점·유형별 임계치·변화율, 매트릭스 가중치·구간·결측 처리, 알림·사건 연결 규칙</t>
+          <t>언제·무엇이 많았나</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>구조만 정의</t>
+          <t>기간별 발생, 유형별 사건 수</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr"/>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>10.2 IA-06 통계</t>
+        </is>
+      </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>지역별 비교</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
+          <t>어디서 많았나</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>구조만 정의</t>
+          <t>지역별 사건 수 · 진행 중 · 첫 대응까지</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>전파 대상</t>
-        </is>
-      </c>
+          <t>이력 · IA-06 통계</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>10.2 IA-06 통계</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>부서·기관·지역·매체·권한</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>숫자는 이력과 같은 사건 원장에서 센다. 조건이 같으면 이력 [사건] 게시판의 건수와 같다. 모든 사건이 가진 값(상태·유형·지역· 발생·첫 대응·종료 시각)으로만 세고, 일부 사건에만 있는 값(위험 등급·전파 건수)은 합계를 흐리므로 통계에 세우지 않는다. 계측 곡선·열돔·수온처럼 사건 원장이 아닌 자료로 그리는 판도 두지 않는다. 사건의 계측은 사건 작업공간의 관측 근거와 이력의 사건 기록이 보인다.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>모델·버전·입출력·유효시간·검증상태</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>구조만 정의</t>
-        </is>
-      </c>
+          <t>현재 사건과 화면의 근거를 요약하고 사용자를 해당 정보로 이동시킨다. 별도의 판단 결과를 만드는 독립 사일로로 두지 않는다.</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>사용자·권한</t>
-        </is>
-      </c>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>역할, 승인권한, 개인정보 접근</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>후속 제품 범위</t>
-        </is>
-      </c>
+          <t>현재 사건 요약과 누락 정보 안내</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>IA-A01</t>
+          <t>IA-G01</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>운영 관리</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr"/>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
+          <t>특정 판단에 사용된 관측·예측·SOP 근거 찾기</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>유사 사건·과거 결정 탐색</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>전파문·상황보고서 초안 작성</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>허용 역할</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>답변 근거가 있는 화면·이벤트·문서로 이동</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>원천에 없는 사실 생성 금지</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>확실성·한계를 숨긴 단정 금지</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>담당자 승인 대행 금지</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>IA-G01</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>공통 AI 보조</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>제한</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>근거 링크 없는 위험도·대응 결론 금지</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr"/>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리 기능은 제품에는 필요하지만 대표 데모 주동선에는 포함하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>데이터 연계</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>원천·주기·권한·상태·스키마 관리</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>위험도·알림 규칙</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>지점·유형별 임계치·변화율, 매트릭스 가중치·구간·결측 처리, 알림·사건 연결 규칙</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>유형·단계별 업무, 자동/승인, 담당 조직</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>전파 대상</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>부서·기관·지역·매체·권한</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr"/>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>모델·버전·입출력·유효시간·검증상태</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>구조만 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr"/>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>사용자·권한</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>역할, 승인권한, 개인정보 접근</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>후속 제품 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>IA-A01</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>운영 관리</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
           <t>관리 화면 수는 대표 데모 성과에 포함하지 않는다.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5866,7 +6370,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Phase 1 서항 자산과 시나리오 Forecast로 시간 조절·대안 선택이 동작하는 예측 화면. 계산 주체·교체 대상은 내부 관리</t>
+          <t>모의훈련의 지난 사건(구항 방파제 월류). 시나리오 Forecast. 수치 경로는 03 §15(있음)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +6402,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>개념 장면(시간·대안 동작, 계산 아님). 대표 사례 산불</t>
+          <t>모의훈련의 지난 사건(무학산 산불). 사전 작성 예측판. 수치 경로는 03 §15(확인 필요)</t>
         </is>
       </c>
     </row>
@@ -5930,14 +6434,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>개념 장면(시간·대안 동작, 계산 아님)</t>
+          <t>모의훈련의 지난 사건(교방동 급경사지 변위). 사전 작성 예측판. 수치 경로는 03 §15(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R0 유형은 계산 결과 화면처럼 만들지 않는다. 필요한 입력·모델과 예상 출력의 차이를 설명하는 정적 개념 예시로만 표현한다.</t>
+          <t>R0 유형은 계산 결과를 주장하지 않는다. 2026-09-16 C~G 를 지난 사건으로 세웠고(03 §5·§16) 모의훈련(IA-07)에서 연다. 값은 사전 작성 예측판이다. 수치는 03 §15 경로 표와 README §2.3 기준 ③을 따르고, 어느 사건을 Phase 2에 보일지는 README §6.1에서 정한다. 실시간 물리 계산처럼 부르지 않고, 모델이 연결되면 같은 계약의 ModelRun 결과로 교체한다.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
@@ -5949,7 +6453,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 처리상태 통제와 도로·시설 통제 Action은 이름이 같아도 서로 다른 값이다.</t>
+          <t>R0~R3은 03_유형별디지털트윈.md의 데이터·모델·업무 준비도다. P0~P2는 02_대표데모시나리오.md의 자료 확인 우선순위다. 사건 국면 안정과 도로·시설 통제 Action은 서로 다른 값이다. 국면의 옛 이름 통제가 Action 과 같은 이름이라 2026-09-16 안정으로 바꿨다.</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
@@ -6067,7 +6571,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>큐에 나타난 후보를 열고 연결 근거 확인</t>
+          <t>실시간 주요 사건에 나타난 후보를 열고 연결 근거 확인</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -6195,7 +6699,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>대안 선택으로 기준 대 대안 비교, [이 전망으로 대응 검토]</t>
+          <t>전망 탭에서 대응 유형·시작 시점을 골라 기준과 견주고 [이 전망으로 조치안 갱신]</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -6281,7 +6785,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IA-05 기록·검증</t>
+          <t>IA-05 이력</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6291,12 +6795,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>종료·검증·보고서</t>
+          <t>사건을 종료하면 이력의 사건 기록 창이 ⑤ 예측 검증 절로 열린다. 위로 올리면 요약·근거·대응, 아래는 경과이고 보고서로 넘어간다</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>/scr-04 → /scr-07?event=...</t>
+          <t>/scr-07?incident=…&amp;view=case</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6477,30 +6981,18 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>scenarioId</t>
+          <t>predictionCaseId</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D8에서 생성한 훈련 시나리오와 원 사건 스냅샷 연결</t>
+          <t>사건의 예측판 하나와 실제 결과·오차의 연결(§13.1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>trainingRunId</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>같은 시나리오의 개별 훈련 실행·결정·결과 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>화면이 각자 사건 상태와 시간을 복제해서 소유하지 않는다.</t>
         </is>
@@ -6517,7 +7009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6783,41 +7275,75 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TrainingScenario</t>
+          <t>PredictionCase</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>IA-05·IA-T01</t>
+          <t>IA-05</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>원 사건 스냅샷·이벤트·Forecast·대응 이력 참조, 훈련 조건·목표·버전</t>
+          <t>원 사건·예측 기준·기준/대안 전망·실제 대응·실제 결과·오차·개선 항목(§13.1)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TrainingRun</t>
+          <t>TrainingScenario</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>IA-T01</t>
+          <t>IA-07</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>시나리오별 실행상태·참여자·훈련 결정·조치·결과·회고</t>
+          <t>지난 사건·분석 기준 시점·바꾼 조건(상황 단계·유형 결합·대응·조정값)·판 참조·상황 부여(03 §26.3·§26.4)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AnalysisResult</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>IA-07</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>분석 결과: 사건·분석 기준 시점·기준·바꾼 조건·결과·개선 항목·메모(03 §26.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ImprovementItem</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>IA-05·07</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>개선 항목: 축(임계치·모델·데이터·SOP)·출처(검증·훈련)·근거 참조·승인 상태. 훈련 출처는 모델 축을 쓰지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>같은 객체를 화면마다 다른 값으로 복제하지 않고, 질문에 맞는 요약만 다르게 보여준다.</t>
         </is>
@@ -7027,7 +7553,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IA-01 사건 우선 큐</t>
+          <t>IA-01 실시간 주요 사건</t>
         </is>
       </c>
     </row>
@@ -7056,12 +7582,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>재편</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>후속 제품 분석 범위</t>
+          <t>IA-06 통계의 유형별·상태별 분포. 사건 원장으로 센다(2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7672,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IA-03 디지털트윈(사건 지도 안) · /scr-05 디지털트윈 메뉴</t>
+          <t>IA-03 디지털트윈(사건 지도 안) · /scr-05 모의훈련(IA-07)</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7706,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>디지털트윈 메뉴의 조건 세트(유형·지역·조건 → 사전 작성 예측판). 상승률 계산은 폐기</t>
+          <t>/scr-05 모의훈련(IA-07 · README §2.3). 사건 없는 조건 시뮬레이션과 상승률 계산은 폐기 유지. 편집기로 만드는 가상 시나리오는 비전(03 §26.9)</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7723,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>E 대기·면 노출의 개념 예시. 03 §23 광역 인셋 재료 (2026-09-15, 앞선 "제외" 대체)</t>
+          <t>03 §23 광역 인셋 부품. 폭염 사건을 모의훈련에 보일지는 README §7 (폭염은 대응이 바꾸는 트윈 결과가 없어 수치 비교가 없다 · 03 §15)</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7757,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IA-04 결과·IA-05 기록</t>
+          <t>IA-04 결과 · IA-05 이력 사건 기록의 ④ 대응과 ⑥ 경과</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7774,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IA-05 기록·검증</t>
+          <t>IA-06 통계. 사건 원장으로 다시 센다. 계측 곡선·열돔·수온 판과 사건 이력 탭은 통계에서 뺀다(2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7786,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IA-05 산출물로 통합 검토</t>
+          <t>IA-05 이력의 [보고서] 탭. 보고서 메뉴는 이력으로 바꿨다(2026-09-16)</t>
         </is>
       </c>
     </row>
